--- a/supervised_results.xlsx
+++ b/supervised_results.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adepa\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adepa\OneDrive\Desktop\Supervised results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B046A5F-8A42-4144-8382-E468B49A286E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59333556-0FC9-409B-BDAC-B4E638AF1DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Foglio1!$AM$92:$AV$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Foglio1!$EK$92:$ET$114</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -691,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -877,18 +877,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1295,91 +1283,91 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="M1:EW236"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" customWidth="1"/>
-    <col min="13" max="13" width="40.6640625" customWidth="1"/>
-    <col min="14" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="8.6640625" customWidth="1"/>
-    <col min="26" max="26" width="40.77734375" customWidth="1"/>
-    <col min="27" max="34" width="8.88671875" customWidth="1"/>
-    <col min="35" max="35" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="40.77734375" customWidth="1"/>
-    <col min="40" max="50" width="8.88671875" customWidth="1"/>
-    <col min="52" max="52" width="8.88671875" customWidth="1"/>
-    <col min="53" max="53" width="40.77734375" customWidth="1"/>
-    <col min="54" max="62" width="8.88671875" customWidth="1"/>
-    <col min="64" max="66" width="8.88671875" customWidth="1"/>
-    <col min="67" max="67" width="40.77734375" customWidth="1"/>
-    <col min="68" max="73" width="8.88671875" customWidth="1"/>
-    <col min="74" max="76" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="81" width="8.88671875" customWidth="1"/>
-    <col min="82" max="82" width="40.77734375" customWidth="1"/>
-    <col min="83" max="88" width="8.88671875" customWidth="1"/>
-    <col min="89" max="90" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="91" max="95" width="8.88671875" customWidth="1"/>
-    <col min="96" max="96" width="40.77734375" customWidth="1"/>
-    <col min="97" max="100" width="8.88671875" customWidth="1"/>
-    <col min="101" max="102" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="103" max="112" width="8.88671875" customWidth="1"/>
-    <col min="114" max="114" width="40.77734375" customWidth="1"/>
-    <col min="115" max="123" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="40.77734375" customWidth="1"/>
-    <col min="129" max="137" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="40.77734375" customWidth="1"/>
-    <col min="142" max="150" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="40.7109375" customWidth="1"/>
+    <col min="14" max="22" width="8.7109375" customWidth="1"/>
+    <col min="23" max="23" width="10.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="40.7109375" customWidth="1"/>
+    <col min="27" max="34" width="8.85546875" customWidth="1"/>
+    <col min="35" max="35" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="40.7109375" customWidth="1"/>
+    <col min="40" max="50" width="8.85546875" customWidth="1"/>
+    <col min="52" max="52" width="8.85546875" customWidth="1"/>
+    <col min="53" max="53" width="40.7109375" customWidth="1"/>
+    <col min="54" max="62" width="8.85546875" customWidth="1"/>
+    <col min="64" max="66" width="8.85546875" customWidth="1"/>
+    <col min="67" max="67" width="40.7109375" customWidth="1"/>
+    <col min="68" max="73" width="8.85546875" customWidth="1"/>
+    <col min="74" max="76" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="81" width="8.85546875" customWidth="1"/>
+    <col min="82" max="82" width="40.7109375" customWidth="1"/>
+    <col min="83" max="88" width="8.85546875" customWidth="1"/>
+    <col min="89" max="90" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="91" max="95" width="8.85546875" customWidth="1"/>
+    <col min="96" max="96" width="40.7109375" customWidth="1"/>
+    <col min="97" max="100" width="8.85546875" customWidth="1"/>
+    <col min="101" max="102" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="112" width="8.85546875" customWidth="1"/>
+    <col min="114" max="114" width="40.7109375" customWidth="1"/>
+    <col min="115" max="123" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="40.7109375" customWidth="1"/>
+    <col min="129" max="137" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="40.7109375" customWidth="1"/>
+    <col min="142" max="150" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1"/>
-    <row r="2" ht="39.9" customHeight="1"/>
-    <row r="3" ht="39.9" customHeight="1"/>
-    <row r="4" ht="39.9" customHeight="1"/>
-    <row r="18" ht="39.9" customHeight="1"/>
+    <row r="2" ht="39.950000000000003" customHeight="1"/>
+    <row r="3" ht="39.950000000000003" customHeight="1"/>
+    <row r="4" ht="39.950000000000003" customHeight="1"/>
+    <row r="18" ht="39.950000000000003" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1"/>
-    <row r="39" spans="13:22" ht="15" thickBot="1"/>
-    <row r="40" spans="13:22" ht="39.9" customHeight="1" thickBot="1">
+    <row r="39" spans="13:22" ht="15.75" thickBot="1"/>
+    <row r="40" spans="13:22" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="M40" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N40" s="86" t="s">
+      <c r="N40" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="O40" s="87"/>
-      <c r="P40" s="87"/>
-      <c r="Q40" s="87"/>
-      <c r="R40" s="87"/>
-      <c r="S40" s="87"/>
-      <c r="T40" s="87"/>
-      <c r="U40" s="87"/>
-      <c r="V40" s="88"/>
+      <c r="O40" s="83"/>
+      <c r="P40" s="83"/>
+      <c r="Q40" s="83"/>
+      <c r="R40" s="83"/>
+      <c r="S40" s="83"/>
+      <c r="T40" s="83"/>
+      <c r="U40" s="83"/>
+      <c r="V40" s="84"/>
     </row>
-    <row r="41" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="41" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M41" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="92" t="s">
+      <c r="N41" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="O41" s="93"/>
-      <c r="P41" s="94"/>
-      <c r="Q41" s="92" t="s">
+      <c r="O41" s="89"/>
+      <c r="P41" s="90"/>
+      <c r="Q41" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="R41" s="93"/>
-      <c r="S41" s="94"/>
-      <c r="T41" s="92" t="s">
+      <c r="R41" s="89"/>
+      <c r="S41" s="90"/>
+      <c r="T41" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="U41" s="93"/>
-      <c r="V41" s="94"/>
+      <c r="U41" s="89"/>
+      <c r="V41" s="90"/>
     </row>
-    <row r="42" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="42" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M42" s="11" t="s">
         <v>28</v>
       </c>
@@ -1411,7 +1399,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="43" spans="13:22" ht="24.9" customHeight="1">
+    <row r="43" spans="13:22" ht="24.95" customHeight="1">
       <c r="M43" s="13" t="s">
         <v>8</v>
       </c>
@@ -1443,7 +1431,7 @@
         <v>0.60499999999999998</v>
       </c>
     </row>
-    <row r="44" spans="13:22" ht="24.9" customHeight="1">
+    <row r="44" spans="13:22" ht="24.95" customHeight="1">
       <c r="M44" s="3" t="s">
         <v>15</v>
       </c>
@@ -1475,39 +1463,39 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="45" spans="13:22" ht="24.9" customHeight="1">
+    <row r="45" spans="13:22" ht="24.95" customHeight="1">
       <c r="M45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="N45" s="32">
-        <v>0.376</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="O45" s="33">
-        <v>0.69199999999999995</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="P45" s="34">
-        <v>0.63200000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="Q45" s="32">
-        <v>0.56399999999999995</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="R45" s="33">
-        <v>0.58099999999999996</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="S45" s="34">
-        <v>0.56100000000000005</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="T45" s="32">
-        <v>0.42799999999999999</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="U45" s="33">
-        <v>0.496</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="V45" s="34">
-        <v>0.46600000000000003</v>
+        <v>0.49099999999999999</v>
       </c>
     </row>
-    <row r="46" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="46" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M46" s="4" t="s">
         <v>22</v>
       </c>
@@ -1539,7 +1527,7 @@
         <v>0.61099999999999999</v>
       </c>
     </row>
-    <row r="47" spans="13:22" ht="24.9" customHeight="1">
+    <row r="47" spans="13:22" ht="24.95" customHeight="1">
       <c r="M47" s="13" t="s">
         <v>9</v>
       </c>
@@ -1571,7 +1559,7 @@
         <v>0.53400000000000003</v>
       </c>
     </row>
-    <row r="48" spans="13:22" ht="24.9" customHeight="1">
+    <row r="48" spans="13:22" ht="24.95" customHeight="1">
       <c r="M48" s="3" t="s">
         <v>16</v>
       </c>
@@ -1603,39 +1591,39 @@
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="49" spans="13:25" ht="24.9" customHeight="1">
+    <row r="49" spans="13:25" ht="24.95" customHeight="1">
       <c r="M49" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N49" s="32">
-        <v>0.76</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="O49" s="33">
-        <v>0.48299999999999998</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="P49" s="34">
-        <v>0.36399999999999999</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="Q49" s="32">
-        <v>0.59299999999999997</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="R49" s="33">
-        <v>0.61699999999999999</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="S49" s="34">
-        <v>0.749</v>
+        <v>0.496</v>
       </c>
       <c r="T49" s="32">
-        <v>0.41699999999999998</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="U49" s="33">
-        <v>0.49</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="V49" s="34">
-        <v>0.44</v>
+        <v>0.51100000000000001</v>
       </c>
     </row>
-    <row r="50" spans="13:25" ht="24.9" customHeight="1" thickBot="1">
+    <row r="50" spans="13:25" ht="24.95" customHeight="1" thickBot="1">
       <c r="M50" s="4" t="s">
         <v>25</v>
       </c>
@@ -1667,7 +1655,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="51" spans="13:25" ht="24.9" customHeight="1">
+    <row r="51" spans="13:25" ht="24.95" customHeight="1">
       <c r="M51" s="13" t="s">
         <v>10</v>
       </c>
@@ -1699,7 +1687,7 @@
         <v>0.61899999999999999</v>
       </c>
     </row>
-    <row r="52" spans="13:25" ht="24.9" customHeight="1">
+    <row r="52" spans="13:25" ht="24.95" customHeight="1">
       <c r="M52" s="3" t="s">
         <v>17</v>
       </c>
@@ -1731,39 +1719,39 @@
         <v>0.55100000000000005</v>
       </c>
     </row>
-    <row r="53" spans="13:25" ht="24.9" customHeight="1">
+    <row r="53" spans="13:25" ht="24.95" customHeight="1">
       <c r="M53" s="3" t="s">
         <v>27</v>
       </c>
       <c r="N53" s="32">
-        <v>0.42899999999999999</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="O53" s="33">
-        <v>0.56999999999999995</v>
+        <v>0.82</v>
       </c>
       <c r="P53" s="34">
+        <v>0.871</v>
+      </c>
+      <c r="Q53" s="32">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="R53" s="33">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="S53" s="34">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="T53" s="32">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="U53" s="33">
         <v>0.47199999999999998</v>
       </c>
-      <c r="Q53" s="32">
-        <v>0.47399999999999998</v>
-      </c>
-      <c r="R53" s="33">
-        <v>0.5</v>
-      </c>
-      <c r="S53" s="34">
-        <v>0.52200000000000002</v>
-      </c>
-      <c r="T53" s="32">
-        <v>0.42799999999999999</v>
-      </c>
-      <c r="U53" s="33">
-        <v>0.41099999999999998</v>
-      </c>
       <c r="V53" s="34">
-        <v>0.46300000000000002</v>
+        <v>0.48599999999999999</v>
       </c>
     </row>
-    <row r="54" spans="13:25" ht="24.9" customHeight="1" thickBot="1">
+    <row r="54" spans="13:25" ht="24.95" customHeight="1" thickBot="1">
       <c r="M54" s="4" t="s">
         <v>26</v>
       </c>
@@ -1795,7 +1783,7 @@
         <v>0.57099999999999995</v>
       </c>
     </row>
-    <row r="55" spans="13:25" ht="24.9" customHeight="1">
+    <row r="55" spans="13:25" ht="24.95" customHeight="1">
       <c r="M55" s="13" t="s">
         <v>11</v>
       </c>
@@ -1827,7 +1815,7 @@
         <v>0.35799999999999998</v>
       </c>
     </row>
-    <row r="56" spans="13:25" ht="24.9" customHeight="1">
+    <row r="56" spans="13:25" ht="24.95" customHeight="1">
       <c r="M56" s="3" t="s">
         <v>18</v>
       </c>
@@ -1859,40 +1847,40 @@
         <v>0.54900000000000004</v>
       </c>
     </row>
-    <row r="57" spans="13:25" ht="24.9" customHeight="1">
+    <row r="57" spans="13:25" ht="24.95" customHeight="1">
       <c r="M57" s="3" t="s">
         <v>20</v>
       </c>
       <c r="N57" s="32">
-        <v>0.375</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="O57" s="33">
-        <v>0.65300000000000002</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="P57" s="34">
-        <v>0.72399999999999998</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="Q57" s="32">
-        <v>0.55700000000000005</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="R57" s="33">
-        <v>0.57499999999999996</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="S57" s="34">
-        <v>0.63</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="T57" s="32">
-        <v>0.47099999999999997</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="U57" s="33">
-        <v>0.50900000000000001</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="V57" s="34">
-        <v>0.495</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="Y57" s="1"/>
     </row>
-    <row r="58" spans="13:25" ht="24.9" customHeight="1" thickBot="1">
+    <row r="58" spans="13:25" ht="24.95" customHeight="1" thickBot="1">
       <c r="M58" s="4" t="s">
         <v>21</v>
       </c>
@@ -1924,7 +1912,7 @@
         <v>0.621</v>
       </c>
     </row>
-    <row r="59" spans="13:25" ht="24.9" customHeight="1">
+    <row r="59" spans="13:25" ht="24.95" customHeight="1">
       <c r="M59" s="2" t="s">
         <v>12</v>
       </c>
@@ -1956,7 +1944,7 @@
         <v>0.628</v>
       </c>
     </row>
-    <row r="60" spans="13:25" ht="24.9" customHeight="1">
+    <row r="60" spans="13:25" ht="24.95" customHeight="1">
       <c r="M60" s="3" t="s">
         <v>19</v>
       </c>
@@ -1988,39 +1976,39 @@
         <v>0.56399999999999995</v>
       </c>
     </row>
-    <row r="61" spans="13:25" ht="24.9" customHeight="1">
+    <row r="61" spans="13:25" ht="24.95" customHeight="1">
       <c r="M61" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N61" s="32">
-        <v>0.35399999999999998</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="O61" s="33">
-        <v>0.755</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="P61" s="34">
-        <v>0.71299999999999997</v>
+        <v>0.59</v>
       </c>
       <c r="Q61" s="32">
-        <v>0.67300000000000004</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="R61" s="33">
-        <v>0.749</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="S61" s="34">
-        <v>0.75</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="T61" s="32">
-        <v>0.45600000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="U61" s="33">
-        <v>0.56999999999999995</v>
+        <v>0.443</v>
       </c>
       <c r="V61" s="34">
-        <v>0.77300000000000002</v>
+        <v>0.57899999999999996</v>
       </c>
     </row>
-    <row r="62" spans="13:25" ht="24.9" customHeight="1" thickBot="1">
+    <row r="62" spans="13:25" ht="24.95" customHeight="1" thickBot="1">
       <c r="M62" s="4" t="s">
         <v>14</v>
       </c>
@@ -2076,7 +2064,7 @@
       <c r="U64" s="12"/>
       <c r="V64" s="12"/>
     </row>
-    <row r="65" spans="13:22" ht="21.6" thickBot="1">
+    <row r="65" spans="13:22" ht="21.75" thickBot="1">
       <c r="M65" s="12"/>
       <c r="N65" s="12"/>
       <c r="O65" s="12"/>
@@ -2088,43 +2076,43 @@
       <c r="U65" s="12"/>
       <c r="V65" s="12"/>
     </row>
-    <row r="66" spans="13:22" ht="39.9" customHeight="1" thickBot="1">
+    <row r="66" spans="13:22" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="M66" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N66" s="97" t="s">
+      <c r="N66" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="O66" s="98"/>
-      <c r="P66" s="98"/>
-      <c r="Q66" s="98"/>
-      <c r="R66" s="98"/>
-      <c r="S66" s="98"/>
-      <c r="T66" s="98"/>
-      <c r="U66" s="98"/>
-      <c r="V66" s="99"/>
+      <c r="O66" s="94"/>
+      <c r="P66" s="94"/>
+      <c r="Q66" s="94"/>
+      <c r="R66" s="94"/>
+      <c r="S66" s="94"/>
+      <c r="T66" s="94"/>
+      <c r="U66" s="94"/>
+      <c r="V66" s="95"/>
     </row>
-    <row r="67" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="67" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M67" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N67" s="89" t="s">
+      <c r="N67" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O67" s="90"/>
-      <c r="P67" s="91"/>
-      <c r="Q67" s="89" t="s">
+      <c r="O67" s="86"/>
+      <c r="P67" s="87"/>
+      <c r="Q67" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="R67" s="90"/>
-      <c r="S67" s="91"/>
-      <c r="T67" s="89" t="s">
+      <c r="R67" s="86"/>
+      <c r="S67" s="87"/>
+      <c r="T67" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="U67" s="90"/>
-      <c r="V67" s="91"/>
+      <c r="U67" s="86"/>
+      <c r="V67" s="87"/>
     </row>
-    <row r="68" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="68" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M68" s="11" t="s">
         <v>28</v>
       </c>
@@ -2156,7 +2144,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="69" spans="13:22" ht="24.9" customHeight="1">
+    <row r="69" spans="13:22" ht="24.95" customHeight="1">
       <c r="M69" s="13" t="s">
         <v>8</v>
       </c>
@@ -2188,7 +2176,7 @@
         <v>0.32400000000000001</v>
       </c>
     </row>
-    <row r="70" spans="13:22" ht="24.9" customHeight="1">
+    <row r="70" spans="13:22" ht="24.95" customHeight="1">
       <c r="M70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2220,39 +2208,39 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="71" spans="13:22" ht="24.9" customHeight="1">
+    <row r="71" spans="13:22" ht="24.95" customHeight="1">
       <c r="M71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="32">
-        <v>0.34200000000000003</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="O71" s="33">
-        <v>0.27700000000000002</v>
+        <v>0.434</v>
       </c>
       <c r="P71" s="34">
-        <v>0.28199999999999997</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="Q71" s="32">
-        <v>0.19900000000000001</v>
+        <v>0.316</v>
       </c>
       <c r="R71" s="33">
-        <v>0.25900000000000001</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="S71" s="34">
-        <v>0.246</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="T71" s="32">
-        <v>0.23799999999999999</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="U71" s="33">
-        <v>0.246</v>
+        <v>0.254</v>
       </c>
       <c r="V71" s="34">
-        <v>0.217</v>
+        <v>0.24399999999999999</v>
       </c>
     </row>
-    <row r="72" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="72" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M72" s="4" t="s">
         <v>22</v>
       </c>
@@ -2284,7 +2272,7 @@
         <v>0.29299999999999998</v>
       </c>
     </row>
-    <row r="73" spans="13:22" ht="24.9" customHeight="1">
+    <row r="73" spans="13:22" ht="24.95" customHeight="1">
       <c r="M73" s="13" t="s">
         <v>9</v>
       </c>
@@ -2316,7 +2304,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="74" spans="13:22" ht="24.9" customHeight="1">
+    <row r="74" spans="13:22" ht="24.95" customHeight="1">
       <c r="M74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2348,39 +2336,39 @@
         <v>0.192</v>
       </c>
     </row>
-    <row r="75" spans="13:22" ht="24.9" customHeight="1">
+    <row r="75" spans="13:22" ht="24.95" customHeight="1">
       <c r="M75" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N75" s="32">
-        <v>0.28999999999999998</v>
+        <v>0.44</v>
       </c>
       <c r="O75" s="33">
-        <v>0.32</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="P75" s="34">
-        <v>0.29299999999999998</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="Q75" s="32">
-        <v>0.183</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="R75" s="33">
-        <v>0.23699999999999999</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="S75" s="34">
-        <v>0.253</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="T75" s="32">
-        <v>0.21299999999999999</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="U75" s="33">
-        <v>0.214</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="V75" s="34">
-        <v>0.25700000000000001</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
-    <row r="76" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="76" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M76" s="4" t="s">
         <v>25</v>
       </c>
@@ -2412,7 +2400,7 @@
         <v>0.30299999999999999</v>
       </c>
     </row>
-    <row r="77" spans="13:22" ht="24.9" customHeight="1">
+    <row r="77" spans="13:22" ht="24.95" customHeight="1">
       <c r="M77" s="13" t="s">
         <v>10</v>
       </c>
@@ -2444,7 +2432,7 @@
         <v>0.20300000000000001</v>
       </c>
     </row>
-    <row r="78" spans="13:22" ht="24.9" customHeight="1">
+    <row r="78" spans="13:22" ht="24.95" customHeight="1">
       <c r="M78" s="3" t="s">
         <v>17</v>
       </c>
@@ -2476,39 +2464,39 @@
         <v>0.20300000000000001</v>
       </c>
     </row>
-    <row r="79" spans="13:22" ht="24.9" customHeight="1">
+    <row r="79" spans="13:22" ht="24.95" customHeight="1">
       <c r="M79" s="3" t="s">
         <v>27</v>
       </c>
       <c r="N79" s="32">
-        <v>7.9000000000000001E-2</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="O79" s="33">
-        <v>0.32600000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="P79" s="34">
-        <v>0.214</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="Q79" s="32">
-        <v>0.161</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="R79" s="33">
-        <v>0.187</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="S79" s="34">
-        <v>0.224</v>
+        <v>0.318</v>
       </c>
       <c r="T79" s="32">
-        <v>0.189</v>
+        <v>0.254</v>
       </c>
       <c r="U79" s="33">
-        <v>0.13800000000000001</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="V79" s="34">
-        <v>0.221</v>
+        <v>0.27100000000000002</v>
       </c>
     </row>
-    <row r="80" spans="13:22" ht="24.9" customHeight="1" thickBot="1">
+    <row r="80" spans="13:22" ht="24.95" customHeight="1" thickBot="1">
       <c r="M80" s="4" t="s">
         <v>26</v>
       </c>
@@ -2540,7 +2528,7 @@
         <v>0.24199999999999999</v>
       </c>
     </row>
-    <row r="81" spans="13:153" ht="24.9" customHeight="1">
+    <row r="81" spans="13:153" ht="24.95" customHeight="1">
       <c r="M81" s="13" t="s">
         <v>11</v>
       </c>
@@ -2572,7 +2560,7 @@
         <v>0.24299999999999999</v>
       </c>
     </row>
-    <row r="82" spans="13:153" ht="24.9" customHeight="1">
+    <row r="82" spans="13:153" ht="24.95" customHeight="1">
       <c r="M82" s="3" t="s">
         <v>18</v>
       </c>
@@ -2604,39 +2592,39 @@
         <v>0.23100000000000001</v>
       </c>
     </row>
-    <row r="83" spans="13:153" ht="24.9" customHeight="1">
+    <row r="83" spans="13:153" ht="24.95" customHeight="1">
       <c r="M83" s="3" t="s">
         <v>20</v>
       </c>
       <c r="N83" s="32">
-        <v>0.252</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="O83" s="33">
-        <v>0.29099999999999998</v>
+        <v>0.433</v>
       </c>
       <c r="P83" s="34">
-        <v>0.28000000000000003</v>
+        <v>0.39</v>
       </c>
       <c r="Q83" s="32">
-        <v>0.217</v>
+        <v>0.314</v>
       </c>
       <c r="R83" s="33">
-        <v>0.26300000000000001</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="S83" s="34">
-        <v>0.26800000000000002</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="T83" s="32">
-        <v>0.249</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="U83" s="33">
-        <v>0.26500000000000001</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="V83" s="34">
-        <v>0.255</v>
+        <v>0.24</v>
       </c>
     </row>
-    <row r="84" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="84" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M84" s="4" t="s">
         <v>21</v>
       </c>
@@ -2668,7 +2656,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="85" spans="13:153" ht="24.9" customHeight="1">
+    <row r="85" spans="13:153" ht="24.95" customHeight="1">
       <c r="M85" s="2" t="s">
         <v>12</v>
       </c>
@@ -2700,7 +2688,7 @@
         <v>0.40600000000000003</v>
       </c>
     </row>
-    <row r="86" spans="13:153" ht="24.9" customHeight="1">
+    <row r="86" spans="13:153" ht="24.95" customHeight="1">
       <c r="M86" s="3" t="s">
         <v>19</v>
       </c>
@@ -2732,39 +2720,39 @@
         <v>0.191</v>
       </c>
     </row>
-    <row r="87" spans="13:153" ht="24.9" customHeight="1">
+    <row r="87" spans="13:153" ht="24.95" customHeight="1">
       <c r="M87" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N87" s="32">
-        <v>0.35499999999999998</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="O87" s="33">
-        <v>0.28399999999999997</v>
+        <v>0.371</v>
       </c>
       <c r="P87" s="34">
-        <v>0.312</v>
+        <v>0.38</v>
       </c>
       <c r="Q87" s="32">
-        <v>0.20200000000000001</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="R87" s="33">
-        <v>0.17100000000000001</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="S87" s="34">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="T87" s="32">
+        <v>0.252</v>
+      </c>
+      <c r="U87" s="33">
         <v>0.221</v>
       </c>
-      <c r="T87" s="32">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="U87" s="33">
-        <v>0.27200000000000002</v>
-      </c>
       <c r="V87" s="34">
-        <v>0.21199999999999999</v>
+        <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="88" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="88" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M88" s="4" t="s">
         <v>14</v>
       </c>
@@ -2820,7 +2808,7 @@
       <c r="U90" s="12"/>
       <c r="V90" s="12"/>
     </row>
-    <row r="91" spans="13:153" ht="21.6" thickBot="1">
+    <row r="91" spans="13:153" ht="21.75" thickBot="1">
       <c r="M91" s="12"/>
       <c r="N91" s="12"/>
       <c r="O91" s="12"/>
@@ -2832,84 +2820,84 @@
       <c r="U91" s="12"/>
       <c r="V91" s="12"/>
     </row>
-    <row r="92" spans="13:153" ht="39.9" customHeight="1" thickBot="1">
+    <row r="92" spans="13:153" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="M92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N92" s="86" t="s">
+      <c r="N92" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="O92" s="87"/>
-      <c r="P92" s="87"/>
-      <c r="Q92" s="87"/>
-      <c r="R92" s="87"/>
-      <c r="S92" s="87"/>
-      <c r="T92" s="87"/>
-      <c r="U92" s="87"/>
-      <c r="V92" s="88"/>
+      <c r="O92" s="83"/>
+      <c r="P92" s="83"/>
+      <c r="Q92" s="83"/>
+      <c r="R92" s="83"/>
+      <c r="S92" s="83"/>
+      <c r="T92" s="83"/>
+      <c r="U92" s="83"/>
+      <c r="V92" s="84"/>
       <c r="Z92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="AA92" s="86" t="s">
+      <c r="AA92" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="AB92" s="87"/>
-      <c r="AC92" s="87"/>
-      <c r="AD92" s="87"/>
-      <c r="AE92" s="87"/>
-      <c r="AF92" s="87"/>
-      <c r="AG92" s="87"/>
-      <c r="AH92" s="87"/>
-      <c r="AI92" s="88"/>
-      <c r="AJ92" s="81"/>
-      <c r="AK92" s="81"/>
-      <c r="AL92" s="81"/>
+      <c r="AB92" s="83"/>
+      <c r="AC92" s="83"/>
+      <c r="AD92" s="83"/>
+      <c r="AE92" s="83"/>
+      <c r="AF92" s="83"/>
+      <c r="AG92" s="83"/>
+      <c r="AH92" s="83"/>
+      <c r="AI92" s="84"/>
+      <c r="AJ92" s="77"/>
+      <c r="AK92" s="77"/>
+      <c r="AL92" s="77"/>
       <c r="AM92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="AN92" s="97" t="s">
+      <c r="AN92" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="AO92" s="98"/>
-      <c r="AP92" s="98"/>
-      <c r="AQ92" s="98"/>
-      <c r="AR92" s="98"/>
-      <c r="AS92" s="98"/>
-      <c r="AT92" s="98"/>
-      <c r="AU92" s="98"/>
-      <c r="AV92" s="99"/>
-      <c r="AW92" s="70"/>
-      <c r="AX92" s="70"/>
-      <c r="AY92" s="70"/>
-      <c r="AZ92" s="70"/>
+      <c r="AO92" s="94"/>
+      <c r="AP92" s="94"/>
+      <c r="AQ92" s="94"/>
+      <c r="AR92" s="94"/>
+      <c r="AS92" s="94"/>
+      <c r="AT92" s="94"/>
+      <c r="AU92" s="94"/>
+      <c r="AV92" s="95"/>
+      <c r="AW92" s="66"/>
+      <c r="AX92" s="66"/>
+      <c r="AY92" s="66"/>
+      <c r="AZ92" s="66"/>
       <c r="BA92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="BB92" s="86" t="s">
+      <c r="BB92" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="BC92" s="87"/>
-      <c r="BD92" s="87"/>
-      <c r="BE92" s="87"/>
-      <c r="BF92" s="87"/>
-      <c r="BG92" s="87"/>
-      <c r="BH92" s="87"/>
-      <c r="BI92" s="87"/>
-      <c r="BJ92" s="88"/>
+      <c r="BC92" s="83"/>
+      <c r="BD92" s="83"/>
+      <c r="BE92" s="83"/>
+      <c r="BF92" s="83"/>
+      <c r="BG92" s="83"/>
+      <c r="BH92" s="83"/>
+      <c r="BI92" s="83"/>
+      <c r="BJ92" s="84"/>
       <c r="BO92" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="BP92" s="106" t="s">
+      <c r="BP92" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="BQ92" s="107"/>
-      <c r="BR92" s="107"/>
-      <c r="BS92" s="108"/>
-      <c r="BT92" s="108"/>
-      <c r="BU92" s="108"/>
-      <c r="BV92" s="108"/>
-      <c r="BW92" s="108"/>
-      <c r="BX92" s="109"/>
+      <c r="BQ92" s="103"/>
+      <c r="BR92" s="103"/>
+      <c r="BS92" s="104"/>
+      <c r="BT92" s="104"/>
+      <c r="BU92" s="104"/>
+      <c r="BV92" s="104"/>
+      <c r="BW92" s="104"/>
+      <c r="BX92" s="105"/>
       <c r="BY92" s="45"/>
       <c r="BZ92" s="45"/>
       <c r="CA92" s="45"/>
@@ -2918,17 +2906,17 @@
       <c r="CD92" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="CE92" s="100" t="s">
+      <c r="CE92" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="CF92" s="101"/>
-      <c r="CG92" s="101"/>
-      <c r="CH92" s="101"/>
-      <c r="CI92" s="101"/>
-      <c r="CJ92" s="101"/>
-      <c r="CK92" s="101"/>
-      <c r="CL92" s="101"/>
-      <c r="CM92" s="102"/>
+      <c r="CF92" s="97"/>
+      <c r="CG92" s="97"/>
+      <c r="CH92" s="97"/>
+      <c r="CI92" s="97"/>
+      <c r="CJ92" s="97"/>
+      <c r="CK92" s="97"/>
+      <c r="CL92" s="97"/>
+      <c r="CM92" s="98"/>
       <c r="CN92" s="42"/>
       <c r="CO92" s="42"/>
       <c r="CP92" s="42"/>
@@ -2936,17 +2924,17 @@
       <c r="CR92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="CS92" s="86" t="s">
+      <c r="CS92" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="CT92" s="87"/>
-      <c r="CU92" s="87"/>
-      <c r="CV92" s="87"/>
-      <c r="CW92" s="87"/>
-      <c r="CX92" s="87"/>
-      <c r="CY92" s="87"/>
-      <c r="CZ92" s="87"/>
-      <c r="DA92" s="88"/>
+      <c r="CT92" s="83"/>
+      <c r="CU92" s="83"/>
+      <c r="CV92" s="83"/>
+      <c r="CW92" s="83"/>
+      <c r="CX92" s="83"/>
+      <c r="CY92" s="83"/>
+      <c r="CZ92" s="83"/>
+      <c r="DA92" s="84"/>
       <c r="DB92" s="42"/>
       <c r="DC92" s="42"/>
       <c r="DD92" s="42"/>
@@ -2958,17 +2946,17 @@
       <c r="DJ92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="DK92" s="95" t="s">
+      <c r="DK92" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="DL92" s="96"/>
-      <c r="DM92" s="96"/>
-      <c r="DN92" s="87"/>
-      <c r="DO92" s="87"/>
-      <c r="DP92" s="87"/>
-      <c r="DQ92" s="87"/>
-      <c r="DR92" s="87"/>
-      <c r="DS92" s="88"/>
+      <c r="DL92" s="92"/>
+      <c r="DM92" s="92"/>
+      <c r="DN92" s="83"/>
+      <c r="DO92" s="83"/>
+      <c r="DP92" s="83"/>
+      <c r="DQ92" s="83"/>
+      <c r="DR92" s="83"/>
+      <c r="DS92" s="84"/>
       <c r="DT92" s="42"/>
       <c r="DU92" s="42"/>
       <c r="DV92" s="42"/>
@@ -2976,136 +2964,136 @@
       <c r="DX92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="DY92" s="97" t="s">
+      <c r="DY92" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="DZ92" s="98"/>
-      <c r="EA92" s="98"/>
-      <c r="EB92" s="98"/>
-      <c r="EC92" s="98"/>
-      <c r="ED92" s="98"/>
-      <c r="EE92" s="98"/>
-      <c r="EF92" s="98"/>
-      <c r="EG92" s="99"/>
+      <c r="DZ92" s="94"/>
+      <c r="EA92" s="94"/>
+      <c r="EB92" s="94"/>
+      <c r="EC92" s="94"/>
+      <c r="ED92" s="94"/>
+      <c r="EE92" s="94"/>
+      <c r="EF92" s="94"/>
+      <c r="EG92" s="95"/>
       <c r="EH92" s="42"/>
       <c r="EI92" s="42"/>
       <c r="EJ92" s="42"/>
       <c r="EK92" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="EL92" s="86" t="s">
+      <c r="EL92" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="EM92" s="87"/>
-      <c r="EN92" s="87"/>
-      <c r="EO92" s="87"/>
-      <c r="EP92" s="87"/>
-      <c r="EQ92" s="87"/>
-      <c r="ER92" s="87"/>
-      <c r="ES92" s="87"/>
-      <c r="ET92" s="88"/>
+      <c r="EM92" s="83"/>
+      <c r="EN92" s="83"/>
+      <c r="EO92" s="83"/>
+      <c r="EP92" s="83"/>
+      <c r="EQ92" s="83"/>
+      <c r="ER92" s="83"/>
+      <c r="ES92" s="83"/>
+      <c r="ET92" s="84"/>
       <c r="EU92" s="42"/>
       <c r="EV92" s="42"/>
       <c r="EW92" s="42"/>
     </row>
-    <row r="93" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="93" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M93" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N93" s="89" t="s">
+      <c r="N93" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="90"/>
-      <c r="P93" s="91"/>
-      <c r="Q93" s="89" t="s">
+      <c r="O93" s="86"/>
+      <c r="P93" s="87"/>
+      <c r="Q93" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="R93" s="90"/>
-      <c r="S93" s="91"/>
-      <c r="T93" s="89" t="s">
+      <c r="R93" s="86"/>
+      <c r="S93" s="87"/>
+      <c r="T93" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="U93" s="90"/>
-      <c r="V93" s="91"/>
+      <c r="U93" s="86"/>
+      <c r="V93" s="87"/>
       <c r="Z93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AA93" s="92" t="s">
+      <c r="AA93" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="AB93" s="93"/>
-      <c r="AC93" s="94"/>
-      <c r="AD93" s="92" t="s">
+      <c r="AB93" s="89"/>
+      <c r="AC93" s="90"/>
+      <c r="AD93" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="AE93" s="93"/>
-      <c r="AF93" s="94"/>
-      <c r="AG93" s="92" t="s">
+      <c r="AE93" s="89"/>
+      <c r="AF93" s="90"/>
+      <c r="AG93" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="AH93" s="93"/>
-      <c r="AI93" s="94"/>
-      <c r="AJ93" s="81"/>
-      <c r="AK93" s="81"/>
-      <c r="AL93" s="81"/>
+      <c r="AH93" s="89"/>
+      <c r="AI93" s="90"/>
+      <c r="AJ93" s="77"/>
+      <c r="AK93" s="77"/>
+      <c r="AL93" s="77"/>
       <c r="AM93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AN93" s="103" t="s">
+      <c r="AN93" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="AO93" s="104"/>
-      <c r="AP93" s="105"/>
-      <c r="AQ93" s="103" t="s">
+      <c r="AO93" s="100"/>
+      <c r="AP93" s="101"/>
+      <c r="AQ93" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="AR93" s="104"/>
-      <c r="AS93" s="105"/>
-      <c r="AT93" s="103" t="s">
+      <c r="AR93" s="100"/>
+      <c r="AS93" s="101"/>
+      <c r="AT93" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="AU93" s="104"/>
-      <c r="AV93" s="105"/>
-      <c r="AW93" s="70"/>
-      <c r="AX93" s="70"/>
-      <c r="AY93" s="70"/>
-      <c r="AZ93" s="70"/>
+      <c r="AU93" s="100"/>
+      <c r="AV93" s="101"/>
+      <c r="AW93" s="66"/>
+      <c r="AX93" s="66"/>
+      <c r="AY93" s="66"/>
+      <c r="AZ93" s="66"/>
       <c r="BA93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BB93" s="103" t="s">
+      <c r="BB93" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="BC93" s="104"/>
-      <c r="BD93" s="105"/>
-      <c r="BE93" s="103" t="s">
+      <c r="BC93" s="100"/>
+      <c r="BD93" s="101"/>
+      <c r="BE93" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="BF93" s="104"/>
-      <c r="BG93" s="105"/>
-      <c r="BH93" s="103" t="s">
+      <c r="BF93" s="100"/>
+      <c r="BG93" s="101"/>
+      <c r="BH93" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="BI93" s="104"/>
-      <c r="BJ93" s="105"/>
+      <c r="BI93" s="100"/>
+      <c r="BJ93" s="101"/>
       <c r="BO93" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="BP93" s="110" t="s">
+      <c r="BP93" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="BQ93" s="111"/>
-      <c r="BR93" s="112"/>
-      <c r="BS93" s="103" t="s">
+      <c r="BQ93" s="107"/>
+      <c r="BR93" s="108"/>
+      <c r="BS93" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="BT93" s="104"/>
-      <c r="BU93" s="105"/>
-      <c r="BV93" s="103" t="s">
+      <c r="BT93" s="100"/>
+      <c r="BU93" s="101"/>
+      <c r="BV93" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="BW93" s="104"/>
-      <c r="BX93" s="105"/>
+      <c r="BW93" s="100"/>
+      <c r="BX93" s="101"/>
       <c r="BY93" s="45"/>
       <c r="BZ93" s="45"/>
       <c r="CA93" s="45"/>
@@ -3114,21 +3102,21 @@
       <c r="CD93" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="CE93" s="103" t="s">
+      <c r="CE93" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="CF93" s="104"/>
-      <c r="CG93" s="105"/>
-      <c r="CH93" s="103" t="s">
+      <c r="CF93" s="100"/>
+      <c r="CG93" s="101"/>
+      <c r="CH93" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="CI93" s="104"/>
-      <c r="CJ93" s="105"/>
-      <c r="CK93" s="104" t="s">
+      <c r="CI93" s="100"/>
+      <c r="CJ93" s="101"/>
+      <c r="CK93" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="CL93" s="104"/>
-      <c r="CM93" s="105"/>
+      <c r="CL93" s="100"/>
+      <c r="CM93" s="101"/>
       <c r="CN93" s="42"/>
       <c r="CO93" s="42"/>
       <c r="CP93" s="42"/>
@@ -3136,21 +3124,21 @@
       <c r="CR93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="CS93" s="92" t="s">
+      <c r="CS93" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="CT93" s="93"/>
-      <c r="CU93" s="94"/>
-      <c r="CV93" s="92" t="s">
+      <c r="CT93" s="89"/>
+      <c r="CU93" s="90"/>
+      <c r="CV93" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="CW93" s="93"/>
-      <c r="CX93" s="94"/>
-      <c r="CY93" s="93" t="s">
+      <c r="CW93" s="89"/>
+      <c r="CX93" s="90"/>
+      <c r="CY93" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="CZ93" s="93"/>
-      <c r="DA93" s="94"/>
+      <c r="CZ93" s="89"/>
+      <c r="DA93" s="90"/>
       <c r="DB93" s="42"/>
       <c r="DC93" s="42"/>
       <c r="DD93" s="42"/>
@@ -3162,21 +3150,21 @@
       <c r="DJ93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="DK93" s="89" t="s">
+      <c r="DK93" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="DL93" s="90"/>
-      <c r="DM93" s="91"/>
-      <c r="DN93" s="92" t="s">
+      <c r="DL93" s="86"/>
+      <c r="DM93" s="87"/>
+      <c r="DN93" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="DO93" s="93"/>
-      <c r="DP93" s="94"/>
-      <c r="DQ93" s="93" t="s">
+      <c r="DO93" s="89"/>
+      <c r="DP93" s="90"/>
+      <c r="DQ93" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="DR93" s="93"/>
-      <c r="DS93" s="94"/>
+      <c r="DR93" s="89"/>
+      <c r="DS93" s="90"/>
       <c r="DT93" s="42"/>
       <c r="DU93" s="42"/>
       <c r="DV93" s="42"/>
@@ -3184,47 +3172,47 @@
       <c r="DX93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="DY93" s="89" t="s">
+      <c r="DY93" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="DZ93" s="90"/>
-      <c r="EA93" s="91"/>
-      <c r="EB93" s="92" t="s">
+      <c r="DZ93" s="86"/>
+      <c r="EA93" s="87"/>
+      <c r="EB93" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="EC93" s="93"/>
-      <c r="ED93" s="94"/>
-      <c r="EE93" s="93" t="s">
+      <c r="EC93" s="89"/>
+      <c r="ED93" s="90"/>
+      <c r="EE93" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="EF93" s="93"/>
-      <c r="EG93" s="94"/>
+      <c r="EF93" s="89"/>
+      <c r="EG93" s="90"/>
       <c r="EH93" s="42"/>
       <c r="EI93" s="42"/>
       <c r="EJ93" s="42"/>
       <c r="EK93" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="EL93" s="89" t="s">
+      <c r="EL93" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="EM93" s="90"/>
-      <c r="EN93" s="91"/>
-      <c r="EO93" s="92" t="s">
+      <c r="EM93" s="86"/>
+      <c r="EN93" s="87"/>
+      <c r="EO93" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="EP93" s="93"/>
-      <c r="EQ93" s="94"/>
-      <c r="ER93" s="93" t="s">
+      <c r="EP93" s="89"/>
+      <c r="EQ93" s="90"/>
+      <c r="ER93" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="ES93" s="93"/>
-      <c r="ET93" s="94"/>
+      <c r="ES93" s="89"/>
+      <c r="ET93" s="90"/>
       <c r="EU93" s="42"/>
       <c r="EV93" s="42"/>
       <c r="EW93" s="42"/>
     </row>
-    <row r="94" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="94" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M94" s="10" t="s">
         <v>28</v>
       </c>
@@ -3285,9 +3273,9 @@
       <c r="AI94" s="16">
         <v>0.9</v>
       </c>
-      <c r="AJ94" s="81"/>
-      <c r="AK94" s="81"/>
-      <c r="AL94" s="81"/>
+      <c r="AJ94" s="77"/>
+      <c r="AK94" s="77"/>
+      <c r="AL94" s="77"/>
       <c r="AM94" s="17" t="s">
         <v>28</v>
       </c>
@@ -3318,10 +3306,10 @@
       <c r="AV94" s="22">
         <v>0.9</v>
       </c>
-      <c r="AW94" s="70"/>
-      <c r="AX94" s="70"/>
-      <c r="AY94" s="70"/>
-      <c r="AZ94" s="70"/>
+      <c r="AW94" s="66"/>
+      <c r="AX94" s="66"/>
+      <c r="AY94" s="66"/>
+      <c r="AZ94" s="66"/>
       <c r="BA94" s="17" t="s">
         <v>28</v>
       </c>
@@ -3560,7 +3548,7 @@
       <c r="EV94" s="42"/>
       <c r="EW94" s="42"/>
     </row>
-    <row r="95" spans="13:153" ht="24.9" customHeight="1">
+    <row r="95" spans="13:153" ht="24.95" customHeight="1">
       <c r="M95" s="13" t="s">
         <v>8</v>
       </c>
@@ -3594,98 +3582,98 @@
       <c r="Z95" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AA95" s="73">
+      <c r="AA95" s="69">
         <v>0.83099999999999996</v>
       </c>
-      <c r="AB95" s="74">
+      <c r="AB95" s="70">
         <v>0.83899999999999997</v>
       </c>
-      <c r="AC95" s="75">
+      <c r="AC95" s="71">
         <v>0.53500000000000003</v>
       </c>
-      <c r="AD95" s="73">
+      <c r="AD95" s="69">
         <v>0.67500000000000004</v>
       </c>
-      <c r="AE95" s="74">
+      <c r="AE95" s="70">
         <v>0.74299999999999999</v>
       </c>
-      <c r="AF95" s="75">
+      <c r="AF95" s="71">
         <v>0.69099999999999995</v>
       </c>
-      <c r="AG95" s="73">
+      <c r="AG95" s="69">
         <v>0.75600000000000001</v>
       </c>
-      <c r="AH95" s="74">
+      <c r="AH95" s="70">
         <v>0.70299999999999996</v>
       </c>
-      <c r="AI95" s="75">
+      <c r="AI95" s="71">
         <v>0.68</v>
       </c>
-      <c r="AJ95" s="82"/>
-      <c r="AK95" s="82"/>
-      <c r="AL95" s="82"/>
+      <c r="AJ95" s="78"/>
+      <c r="AK95" s="78"/>
+      <c r="AL95" s="78"/>
       <c r="AM95" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="AN95" s="73">
+      <c r="AN95" s="69">
         <v>0.51800000000000002</v>
       </c>
-      <c r="AO95" s="74">
+      <c r="AO95" s="70">
         <v>0.502</v>
       </c>
-      <c r="AP95" s="75">
+      <c r="AP95" s="71">
         <v>0.46200000000000002</v>
       </c>
-      <c r="AQ95" s="73">
+      <c r="AQ95" s="69">
         <v>0.432</v>
       </c>
-      <c r="AR95" s="74">
+      <c r="AR95" s="70">
         <v>0.42299999999999999</v>
       </c>
-      <c r="AS95" s="75">
+      <c r="AS95" s="71">
         <v>0.42499999999999999</v>
       </c>
-      <c r="AT95" s="73">
+      <c r="AT95" s="69">
         <v>0.46600000000000003</v>
       </c>
-      <c r="AU95" s="74">
+      <c r="AU95" s="70">
         <v>0.45300000000000001</v>
       </c>
-      <c r="AV95" s="75">
+      <c r="AV95" s="71">
         <v>0.433</v>
       </c>
-      <c r="AW95" s="71"/>
-      <c r="AX95" s="71"/>
-      <c r="AY95" s="71"/>
-      <c r="AZ95" s="71"/>
+      <c r="AW95" s="67"/>
+      <c r="AX95" s="67"/>
+      <c r="AY95" s="67"/>
+      <c r="AZ95" s="67"/>
       <c r="BA95" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="BB95" s="73">
+      <c r="BB95" s="69">
         <v>0.33400000000000002</v>
       </c>
-      <c r="BC95" s="74">
+      <c r="BC95" s="70">
         <v>0.32100000000000001</v>
       </c>
-      <c r="BD95" s="75">
+      <c r="BD95" s="71">
         <v>0.28799999999999998</v>
       </c>
-      <c r="BE95" s="73">
+      <c r="BE95" s="69">
         <v>0.255</v>
       </c>
-      <c r="BF95" s="74">
+      <c r="BF95" s="70">
         <v>0.25800000000000001</v>
       </c>
-      <c r="BG95" s="75">
+      <c r="BG95" s="71">
         <v>0.25700000000000001</v>
       </c>
-      <c r="BH95" s="73">
+      <c r="BH95" s="69">
         <v>0.27</v>
       </c>
-      <c r="BI95" s="74">
+      <c r="BI95" s="70">
         <v>0.26400000000000001</v>
       </c>
-      <c r="BJ95" s="75">
+      <c r="BJ95" s="71">
         <v>0.26800000000000002</v>
       </c>
       <c r="BO95" s="47" t="s">
@@ -3896,7 +3884,7 @@
       <c r="EV95" s="42"/>
       <c r="EW95" s="42"/>
     </row>
-    <row r="96" spans="13:153" ht="24.9" customHeight="1">
+    <row r="96" spans="13:153" ht="24.95" customHeight="1">
       <c r="M96" s="3" t="s">
         <v>15</v>
       </c>
@@ -3930,98 +3918,98 @@
       <c r="Z96" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AA96" s="76">
+      <c r="AA96" s="72">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AB96" s="77">
+      <c r="AB96" s="73">
         <v>0.53500000000000003</v>
       </c>
-      <c r="AC96" s="78">
+      <c r="AC96" s="74">
         <v>0.80300000000000005</v>
       </c>
-      <c r="AD96" s="76">
+      <c r="AD96" s="72">
         <v>0.66900000000000004</v>
       </c>
-      <c r="AE96" s="77">
+      <c r="AE96" s="73">
         <v>0.65100000000000002</v>
       </c>
-      <c r="AF96" s="78">
+      <c r="AF96" s="74">
         <v>0.64200000000000002</v>
       </c>
-      <c r="AG96" s="76">
+      <c r="AG96" s="72">
         <v>0.69599999999999995</v>
       </c>
-      <c r="AH96" s="77">
+      <c r="AH96" s="73">
         <v>0.66800000000000004</v>
       </c>
-      <c r="AI96" s="78">
+      <c r="AI96" s="74">
         <v>0.63500000000000001</v>
       </c>
-      <c r="AJ96" s="82"/>
-      <c r="AK96" s="82"/>
-      <c r="AL96" s="82"/>
+      <c r="AJ96" s="78"/>
+      <c r="AK96" s="78"/>
+      <c r="AL96" s="78"/>
       <c r="AM96" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AN96" s="76">
+      <c r="AN96" s="72">
         <v>0.52</v>
       </c>
-      <c r="AO96" s="77">
+      <c r="AO96" s="73">
         <v>0.49</v>
       </c>
-      <c r="AP96" s="78">
+      <c r="AP96" s="74">
         <v>0.45600000000000002</v>
       </c>
-      <c r="AQ96" s="76">
+      <c r="AQ96" s="72">
         <v>0.41299999999999998</v>
       </c>
-      <c r="AR96" s="77">
+      <c r="AR96" s="73">
         <v>0.371</v>
       </c>
-      <c r="AS96" s="78">
+      <c r="AS96" s="74">
         <v>0.36199999999999999</v>
       </c>
-      <c r="AT96" s="76">
+      <c r="AT96" s="72">
         <v>0.38200000000000001</v>
       </c>
-      <c r="AU96" s="77">
+      <c r="AU96" s="73">
         <v>0.375</v>
       </c>
-      <c r="AV96" s="78">
+      <c r="AV96" s="74">
         <v>0.36199999999999999</v>
       </c>
-      <c r="AW96" s="71"/>
-      <c r="AX96" s="71"/>
-      <c r="AY96" s="71"/>
-      <c r="AZ96" s="71"/>
+      <c r="AW96" s="67"/>
+      <c r="AX96" s="67"/>
+      <c r="AY96" s="67"/>
+      <c r="AZ96" s="67"/>
       <c r="BA96" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="BB96" s="76">
+      <c r="BB96" s="72">
         <v>0.32300000000000001</v>
       </c>
-      <c r="BC96" s="77">
+      <c r="BC96" s="73">
         <v>0.29699999999999999</v>
       </c>
-      <c r="BD96" s="78">
+      <c r="BD96" s="74">
         <v>0.28199999999999997</v>
       </c>
-      <c r="BE96" s="76">
+      <c r="BE96" s="72">
         <v>0.26300000000000001</v>
       </c>
-      <c r="BF96" s="77">
+      <c r="BF96" s="73">
         <v>0.25</v>
       </c>
-      <c r="BG96" s="78">
+      <c r="BG96" s="74">
         <v>0.224</v>
       </c>
-      <c r="BH96" s="76">
+      <c r="BH96" s="72">
         <v>0.255</v>
       </c>
-      <c r="BI96" s="77">
+      <c r="BI96" s="73">
         <v>0.248</v>
       </c>
-      <c r="BJ96" s="78">
+      <c r="BJ96" s="74">
         <v>0.23899999999999999</v>
       </c>
       <c r="BO96" s="48" t="s">
@@ -4232,21 +4220,21 @@
       <c r="EV96" s="42"/>
       <c r="EW96" s="42"/>
     </row>
-    <row r="97" spans="13:153" ht="24.9" customHeight="1">
+    <row r="97" spans="13:153" ht="24.95" customHeight="1">
       <c r="M97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="N97" s="32">
-        <v>0.23200000000000001</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="O97" s="33">
-        <v>9.2999999999999999E-2</v>
+        <v>0.251</v>
       </c>
       <c r="P97" s="34">
-        <v>0.245</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="Q97" s="32">
-        <v>0.22500000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="R97" s="33">
         <v>0.189</v>
@@ -4255,140 +4243,140 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="T97" s="32">
-        <v>0.13</v>
+        <v>0.186</v>
       </c>
       <c r="U97" s="33">
-        <v>0.161</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="V97" s="34">
-        <v>0.154</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="Z97" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA97" s="76">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="AB97" s="77">
-        <v>0.64800000000000002</v>
-      </c>
-      <c r="AC97" s="78">
-        <v>0.67100000000000004</v>
-      </c>
-      <c r="AD97" s="76">
-        <v>0.58199999999999996</v>
-      </c>
-      <c r="AE97" s="77">
-        <v>0.59299999999999997</v>
-      </c>
-      <c r="AF97" s="78">
-        <v>0.59299999999999997</v>
-      </c>
-      <c r="AG97" s="76">
-        <v>0.55300000000000005</v>
-      </c>
-      <c r="AH97" s="77">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="AI97" s="78">
-        <v>0.56299999999999994</v>
-      </c>
-      <c r="AJ97" s="82"/>
-      <c r="AK97" s="82"/>
-      <c r="AL97" s="82"/>
+      <c r="AA97" s="72">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="AB97" s="73">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="AC97" s="74">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="AD97" s="72">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="AE97" s="73">
+        <v>0.624</v>
+      </c>
+      <c r="AF97" s="74">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="AG97" s="72">
+        <v>0.63</v>
+      </c>
+      <c r="AH97" s="73">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="AI97" s="74">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="AJ97" s="78"/>
+      <c r="AK97" s="78"/>
+      <c r="AL97" s="78"/>
       <c r="AM97" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="AN97" s="76">
-        <v>0.33700000000000002</v>
-      </c>
-      <c r="AO97" s="77">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="AP97" s="78">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="AQ97" s="76">
-        <v>0.30299999999999999</v>
-      </c>
-      <c r="AR97" s="77">
-        <v>0.308</v>
-      </c>
-      <c r="AS97" s="78">
-        <v>0.32900000000000001</v>
-      </c>
-      <c r="AT97" s="76">
-        <v>0.34399999999999997</v>
-      </c>
-      <c r="AU97" s="77">
-        <v>0.34799999999999998</v>
-      </c>
-      <c r="AV97" s="78">
-        <v>0.34699999999999998</v>
-      </c>
-      <c r="AW97" s="71"/>
-      <c r="AX97" s="71"/>
-      <c r="AY97" s="71"/>
-      <c r="AZ97" s="71"/>
+      <c r="AN97" s="72">
+        <v>0.376</v>
+      </c>
+      <c r="AO97" s="73">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="AP97" s="74">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="AQ97" s="72">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="AR97" s="73">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="AS97" s="74">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="AT97" s="72">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="AU97" s="73">
+        <v>0.375</v>
+      </c>
+      <c r="AV97" s="74">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="AW97" s="67"/>
+      <c r="AX97" s="67"/>
+      <c r="AY97" s="67"/>
+      <c r="AZ97" s="67"/>
       <c r="BA97" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="BB97" s="76">
-        <v>0.25</v>
-      </c>
-      <c r="BC97" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="BD97" s="78">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="BE97" s="76">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="BF97" s="77">
+      <c r="BB97" s="72">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="BC97" s="73">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="BD97" s="74">
+        <v>0.255</v>
+      </c>
+      <c r="BE97" s="72">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="BF97" s="73">
         <v>0.23699999999999999</v>
       </c>
-      <c r="BG97" s="78">
-        <v>0.23899999999999999</v>
-      </c>
-      <c r="BH97" s="76">
-        <v>0.22700000000000001</v>
-      </c>
-      <c r="BI97" s="77">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="BJ97" s="78">
-        <v>0.23</v>
+      <c r="BG97" s="74">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="BH97" s="72">
+        <v>0.27</v>
+      </c>
+      <c r="BI97" s="73">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="BJ97" s="74">
+        <v>0.248</v>
       </c>
       <c r="BO97" s="48" t="s">
         <v>23</v>
       </c>
       <c r="BP97" s="62">
-        <v>0.84499999999999997</v>
+        <v>0.95</v>
       </c>
       <c r="BQ97" s="43">
-        <v>0.69199999999999995</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="BR97" s="54">
-        <v>0.36599999999999999</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="BS97" s="62">
-        <v>0.81899999999999995</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="BT97" s="43">
-        <v>0.58099999999999996</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="BU97" s="54">
-        <v>0.34599999999999997</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="BV97" s="62">
-        <v>0.68</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="BW97" s="43">
-        <v>0.496</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="BX97" s="54">
-        <v>0.36499999999999999</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="BY97" s="45"/>
       <c r="BZ97" s="45"/>
@@ -4399,31 +4387,31 @@
         <v>23</v>
       </c>
       <c r="CE97" s="62">
-        <v>0.498</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="CF97" s="43">
-        <v>0.27700000000000002</v>
+        <v>0.434</v>
       </c>
       <c r="CG97" s="54">
-        <v>0.22500000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="CH97" s="62">
-        <v>0.374</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="CI97" s="43">
-        <v>0.25900000000000001</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="CJ97" s="54">
-        <v>0.187</v>
+        <v>0.253</v>
       </c>
       <c r="CK97" s="59">
-        <v>0.44400000000000001</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="CL97" s="43">
-        <v>0.246</v>
+        <v>0.254</v>
       </c>
       <c r="CM97" s="54">
-        <v>0.159</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="CN97" s="42"/>
       <c r="CO97" s="42"/>
@@ -4433,31 +4421,31 @@
         <v>23</v>
       </c>
       <c r="CS97" s="62">
-        <v>0.38600000000000001</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="CT97" s="43">
-        <v>9.2999999999999999E-2</v>
+        <v>0.251</v>
       </c>
       <c r="CU97" s="54">
-        <v>0.19600000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="CV97" s="62">
-        <v>0.28000000000000003</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="CW97" s="43">
         <v>0.189</v>
       </c>
       <c r="CX97" s="54">
-        <v>0.11899999999999999</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="CY97" s="59">
-        <v>0.22</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="CZ97" s="43">
-        <v>0.161</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="DA97" s="54">
-        <v>9.9000000000000005E-2</v>
+        <v>0.121</v>
       </c>
       <c r="DB97" s="42"/>
       <c r="DC97" s="42"/>
@@ -4471,31 +4459,31 @@
         <v>23</v>
       </c>
       <c r="DK97" s="62">
-        <v>0.79800000000000004</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="DL97" s="43">
-        <v>0.64800000000000002</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="DM97" s="54">
-        <v>0.42199999999999999</v>
+        <v>0.61199999999999999</v>
       </c>
       <c r="DN97" s="62">
-        <v>0.81499999999999995</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="DO97" s="43">
-        <v>0.59299999999999997</v>
+        <v>0.624</v>
       </c>
       <c r="DP97" s="54">
-        <v>0.37</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="DQ97" s="59">
-        <v>0.79100000000000004</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="DR97" s="43">
-        <v>0.58399999999999996</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="DS97" s="54">
-        <v>0.434</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="DT97" s="42"/>
       <c r="DU97" s="42"/>
@@ -4505,31 +4493,31 @@
         <v>23</v>
       </c>
       <c r="DY97" s="62">
-        <v>0.53400000000000003</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="DZ97" s="43">
-        <v>0.30099999999999999</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="EA97" s="54">
-        <v>0.24399999999999999</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="EB97" s="62">
-        <v>0.49299999999999999</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="EC97" s="43">
-        <v>0.308</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="ED97" s="54">
-        <v>0.23</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="EE97" s="59">
-        <v>0.56399999999999995</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="EF97" s="43">
-        <v>0.34799999999999998</v>
+        <v>0.375</v>
       </c>
       <c r="EG97" s="54">
-        <v>0.23799999999999999</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="EH97" s="42"/>
       <c r="EI97" s="42"/>
@@ -4538,37 +4526,37 @@
         <v>23</v>
       </c>
       <c r="EL97" s="62">
-        <v>0.40899999999999997</v>
+        <v>0.436</v>
       </c>
       <c r="EM97" s="43">
-        <v>0.1</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="EN97" s="54">
-        <v>0.20499999999999999</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="EO97" s="62">
-        <v>0.35099999999999998</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="EP97" s="43">
         <v>0.23699999999999999</v>
       </c>
       <c r="EQ97" s="54">
-        <v>0.153</v>
+        <v>0.161</v>
       </c>
       <c r="ER97" s="59">
-        <v>0.33300000000000002</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="ES97" s="43">
-        <v>0.24099999999999999</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="ET97" s="54">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="EU97" s="42"/>
       <c r="EV97" s="42"/>
       <c r="EW97" s="42"/>
     </row>
-    <row r="98" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="98" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M98" s="4" t="s">
         <v>22</v>
       </c>
@@ -4602,98 +4590,98 @@
       <c r="Z98" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AA98" s="79">
+      <c r="AA98" s="75">
         <v>0.83499999999999996</v>
       </c>
-      <c r="AB98" s="80">
+      <c r="AB98" s="76">
         <v>0.82699999999999996</v>
       </c>
-      <c r="AC98" s="72">
+      <c r="AC98" s="68">
         <v>0.85</v>
       </c>
-      <c r="AD98" s="79">
+      <c r="AD98" s="75">
         <v>0.65900000000000003</v>
       </c>
-      <c r="AE98" s="80">
+      <c r="AE98" s="76">
         <v>0.76200000000000001</v>
       </c>
-      <c r="AF98" s="72">
+      <c r="AF98" s="68">
         <v>0.67200000000000004</v>
       </c>
-      <c r="AG98" s="79">
+      <c r="AG98" s="75">
         <v>0.70599999999999996</v>
       </c>
-      <c r="AH98" s="80">
+      <c r="AH98" s="76">
         <v>0.66900000000000004</v>
       </c>
-      <c r="AI98" s="72">
+      <c r="AI98" s="68">
         <v>0.68400000000000005</v>
       </c>
-      <c r="AJ98" s="82"/>
-      <c r="AK98" s="82"/>
-      <c r="AL98" s="82"/>
+      <c r="AJ98" s="78"/>
+      <c r="AK98" s="78"/>
+      <c r="AL98" s="78"/>
       <c r="AM98" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AN98" s="79">
+      <c r="AN98" s="75">
         <v>0.48499999999999999</v>
       </c>
-      <c r="AO98" s="80">
+      <c r="AO98" s="76">
         <v>0.48499999999999999</v>
       </c>
-      <c r="AP98" s="72">
+      <c r="AP98" s="68">
         <v>0.45600000000000002</v>
       </c>
-      <c r="AQ98" s="79">
+      <c r="AQ98" s="75">
         <v>0.47199999999999998</v>
       </c>
-      <c r="AR98" s="80">
+      <c r="AR98" s="76">
         <v>0.44400000000000001</v>
       </c>
-      <c r="AS98" s="72">
+      <c r="AS98" s="68">
         <v>0.47799999999999998</v>
       </c>
-      <c r="AT98" s="79">
+      <c r="AT98" s="75">
         <v>0.46200000000000002</v>
       </c>
-      <c r="AU98" s="80">
+      <c r="AU98" s="76">
         <v>0.42199999999999999</v>
       </c>
-      <c r="AV98" s="72">
+      <c r="AV98" s="68">
         <v>0.41599999999999998</v>
       </c>
-      <c r="AW98" s="71"/>
-      <c r="AX98" s="71"/>
-      <c r="AY98" s="71"/>
-      <c r="AZ98" s="71"/>
+      <c r="AW98" s="67"/>
+      <c r="AX98" s="67"/>
+      <c r="AY98" s="67"/>
+      <c r="AZ98" s="67"/>
       <c r="BA98" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="BB98" s="79">
+      <c r="BB98" s="75">
         <v>0.31900000000000001</v>
       </c>
-      <c r="BC98" s="80">
+      <c r="BC98" s="76">
         <v>0.32200000000000001</v>
       </c>
-      <c r="BD98" s="72">
+      <c r="BD98" s="68">
         <v>0.29499999999999998</v>
       </c>
-      <c r="BE98" s="79">
+      <c r="BE98" s="75">
         <v>0.27800000000000002</v>
       </c>
-      <c r="BF98" s="80">
+      <c r="BF98" s="76">
         <v>0.26900000000000002</v>
       </c>
-      <c r="BG98" s="72">
+      <c r="BG98" s="68">
         <v>0.25600000000000001</v>
       </c>
-      <c r="BH98" s="79">
+      <c r="BH98" s="75">
         <v>0.26800000000000002</v>
       </c>
-      <c r="BI98" s="80">
+      <c r="BI98" s="76">
         <v>0.27900000000000003</v>
       </c>
-      <c r="BJ98" s="72">
+      <c r="BJ98" s="68">
         <v>0.25800000000000001</v>
       </c>
       <c r="BO98" s="49" t="s">
@@ -4904,7 +4892,7 @@
       <c r="EV98" s="42"/>
       <c r="EW98" s="42"/>
     </row>
-    <row r="99" spans="13:153" ht="24.9" customHeight="1">
+    <row r="99" spans="13:153" ht="24.95" customHeight="1">
       <c r="M99" s="13" t="s">
         <v>9</v>
       </c>
@@ -4938,98 +4926,98 @@
       <c r="Z99" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AA99" s="73">
+      <c r="AA99" s="69">
         <v>0.72799999999999998</v>
       </c>
-      <c r="AB99" s="74">
+      <c r="AB99" s="70">
         <v>0.76300000000000001</v>
       </c>
-      <c r="AC99" s="75">
+      <c r="AC99" s="71">
         <v>0.752</v>
       </c>
-      <c r="AD99" s="73">
+      <c r="AD99" s="69">
         <v>0.629</v>
       </c>
-      <c r="AE99" s="74">
+      <c r="AE99" s="70">
         <v>0.56200000000000006</v>
       </c>
-      <c r="AF99" s="75">
+      <c r="AF99" s="71">
         <v>0.62</v>
       </c>
-      <c r="AG99" s="73">
+      <c r="AG99" s="69">
         <v>0.64200000000000002</v>
       </c>
-      <c r="AH99" s="74">
+      <c r="AH99" s="70">
         <v>0.59399999999999997</v>
       </c>
-      <c r="AI99" s="75">
+      <c r="AI99" s="71">
         <v>0.58799999999999997</v>
       </c>
-      <c r="AJ99" s="82"/>
-      <c r="AK99" s="82"/>
-      <c r="AL99" s="82"/>
+      <c r="AJ99" s="78"/>
+      <c r="AK99" s="78"/>
+      <c r="AL99" s="78"/>
       <c r="AM99" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="AN99" s="73">
+      <c r="AN99" s="69">
         <v>0.42</v>
       </c>
-      <c r="AO99" s="74">
+      <c r="AO99" s="70">
         <v>0.39100000000000001</v>
       </c>
-      <c r="AP99" s="75">
+      <c r="AP99" s="71">
         <v>0.37</v>
       </c>
-      <c r="AQ99" s="73">
+      <c r="AQ99" s="69">
         <v>0.35599999999999998</v>
       </c>
-      <c r="AR99" s="74">
+      <c r="AR99" s="70">
         <v>0.34699999999999998</v>
       </c>
-      <c r="AS99" s="75">
+      <c r="AS99" s="71">
         <v>0.35399999999999998</v>
       </c>
-      <c r="AT99" s="73">
+      <c r="AT99" s="69">
         <v>0.32700000000000001</v>
       </c>
-      <c r="AU99" s="74">
+      <c r="AU99" s="70">
         <v>0.34399999999999997</v>
       </c>
-      <c r="AV99" s="75">
+      <c r="AV99" s="71">
         <v>0.32700000000000001</v>
       </c>
-      <c r="AW99" s="71"/>
-      <c r="AX99" s="71"/>
-      <c r="AY99" s="71"/>
-      <c r="AZ99" s="71"/>
+      <c r="AW99" s="67"/>
+      <c r="AX99" s="67"/>
+      <c r="AY99" s="67"/>
+      <c r="AZ99" s="67"/>
       <c r="BA99" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="BB99" s="73">
+      <c r="BB99" s="69">
         <v>0.28699999999999998</v>
       </c>
-      <c r="BC99" s="74">
+      <c r="BC99" s="70">
         <v>0.307</v>
       </c>
-      <c r="BD99" s="75">
+      <c r="BD99" s="71">
         <v>0.26300000000000001</v>
       </c>
-      <c r="BE99" s="73">
+      <c r="BE99" s="69">
         <v>0.20499999999999999</v>
       </c>
-      <c r="BF99" s="74">
+      <c r="BF99" s="70">
         <v>0.187</v>
       </c>
-      <c r="BG99" s="75">
+      <c r="BG99" s="71">
         <v>0.19400000000000001</v>
       </c>
-      <c r="BH99" s="73">
+      <c r="BH99" s="69">
         <v>0.23699999999999999</v>
       </c>
-      <c r="BI99" s="74">
+      <c r="BI99" s="70">
         <v>0.24099999999999999</v>
       </c>
-      <c r="BJ99" s="75">
+      <c r="BJ99" s="71">
         <v>0.17100000000000001</v>
       </c>
       <c r="BO99" s="47" t="s">
@@ -5240,7 +5228,7 @@
       <c r="EV99" s="42"/>
       <c r="EW99" s="42"/>
     </row>
-    <row r="100" spans="13:153" ht="24.9" customHeight="1">
+    <row r="100" spans="13:153" ht="24.95" customHeight="1">
       <c r="M100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5274,98 +5262,98 @@
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA100" s="76">
+      <c r="AA100" s="72">
         <v>0.79300000000000004</v>
       </c>
-      <c r="AB100" s="77">
+      <c r="AB100" s="73">
         <v>0.81100000000000005</v>
       </c>
-      <c r="AC100" s="78">
+      <c r="AC100" s="74">
         <v>0.82499999999999996</v>
       </c>
-      <c r="AD100" s="76">
+      <c r="AD100" s="72">
         <v>0.74</v>
       </c>
-      <c r="AE100" s="77">
+      <c r="AE100" s="73">
         <v>0.61499999999999999</v>
       </c>
-      <c r="AF100" s="78">
+      <c r="AF100" s="74">
         <v>0.628</v>
       </c>
-      <c r="AG100" s="76">
+      <c r="AG100" s="72">
         <v>0.66900000000000004</v>
       </c>
-      <c r="AH100" s="77">
+      <c r="AH100" s="73">
         <v>0.55200000000000005</v>
       </c>
-      <c r="AI100" s="78">
+      <c r="AI100" s="74">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AJ100" s="82"/>
-      <c r="AK100" s="82"/>
-      <c r="AL100" s="82"/>
+      <c r="AJ100" s="78"/>
+      <c r="AK100" s="78"/>
+      <c r="AL100" s="78"/>
       <c r="AM100" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="AN100" s="76">
+      <c r="AN100" s="72">
         <v>0.43099999999999999</v>
       </c>
-      <c r="AO100" s="77">
+      <c r="AO100" s="73">
         <v>0.44600000000000001</v>
       </c>
-      <c r="AP100" s="78">
+      <c r="AP100" s="74">
         <v>0.45200000000000001</v>
       </c>
-      <c r="AQ100" s="76">
+      <c r="AQ100" s="72">
         <v>0.39100000000000001</v>
       </c>
-      <c r="AR100" s="77">
+      <c r="AR100" s="73">
         <v>0.38500000000000001</v>
       </c>
-      <c r="AS100" s="78">
+      <c r="AS100" s="74">
         <v>0.377</v>
       </c>
-      <c r="AT100" s="76">
+      <c r="AT100" s="72">
         <v>0.35499999999999998</v>
       </c>
-      <c r="AU100" s="77">
+      <c r="AU100" s="73">
         <v>0.36799999999999999</v>
       </c>
-      <c r="AV100" s="78">
+      <c r="AV100" s="74">
         <v>0.32600000000000001</v>
       </c>
-      <c r="AW100" s="71"/>
-      <c r="AX100" s="71"/>
-      <c r="AY100" s="71"/>
-      <c r="AZ100" s="71"/>
+      <c r="AW100" s="67"/>
+      <c r="AX100" s="67"/>
+      <c r="AY100" s="67"/>
+      <c r="AZ100" s="67"/>
       <c r="BA100" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="BB100" s="76">
+      <c r="BB100" s="72">
         <v>0.316</v>
       </c>
-      <c r="BC100" s="77">
+      <c r="BC100" s="73">
         <v>0.28599999999999998</v>
       </c>
-      <c r="BD100" s="78">
+      <c r="BD100" s="74">
         <v>0.27800000000000002</v>
       </c>
-      <c r="BE100" s="76">
+      <c r="BE100" s="72">
         <v>0.20100000000000001</v>
       </c>
-      <c r="BF100" s="77">
+      <c r="BF100" s="73">
         <v>0.25</v>
       </c>
-      <c r="BG100" s="78">
+      <c r="BG100" s="74">
         <v>0.157</v>
       </c>
-      <c r="BH100" s="76">
+      <c r="BH100" s="72">
         <v>0.26400000000000001</v>
       </c>
-      <c r="BI100" s="77">
+      <c r="BI100" s="73">
         <v>0.23799999999999999</v>
       </c>
-      <c r="BJ100" s="78">
+      <c r="BJ100" s="74">
         <v>0.223</v>
       </c>
       <c r="BO100" s="48" t="s">
@@ -5576,163 +5564,163 @@
       <c r="EV100" s="42"/>
       <c r="EW100" s="42"/>
     </row>
-    <row r="101" spans="13:153" ht="24.9" customHeight="1">
+    <row r="101" spans="13:153" ht="24.95" customHeight="1">
       <c r="M101" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N101" s="32">
-        <v>0.17699999999999999</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="O101" s="33">
-        <v>0.214</v>
+        <v>7.8E-2</v>
       </c>
       <c r="P101" s="34">
-        <v>0.10299999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="Q101" s="32">
-        <v>0.17299999999999999</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="R101" s="33">
-        <v>0.13700000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="S101" s="34">
-        <v>0.14299999999999999</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="T101" s="32">
-        <v>0.124</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="U101" s="33">
-        <v>0.11799999999999999</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="V101" s="34">
-        <v>0.161</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA101" s="76">
-        <v>0.67900000000000005</v>
-      </c>
-      <c r="AB101" s="77">
-        <v>0.57499999999999996</v>
-      </c>
-      <c r="AC101" s="78">
-        <v>0.46</v>
-      </c>
-      <c r="AD101" s="76">
-        <v>0.58099999999999996</v>
-      </c>
-      <c r="AE101" s="77">
-        <v>0.62</v>
-      </c>
-      <c r="AF101" s="78">
-        <v>0.67800000000000005</v>
-      </c>
-      <c r="AG101" s="76">
-        <v>0.501</v>
-      </c>
-      <c r="AH101" s="77">
-        <v>0.53500000000000003</v>
-      </c>
-      <c r="AI101" s="78">
-        <v>0.54100000000000004</v>
-      </c>
-      <c r="AJ101" s="82"/>
-      <c r="AK101" s="82"/>
-      <c r="AL101" s="82"/>
+      <c r="AA101" s="72">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="AB101" s="73">
+        <v>0.74099999999999999</v>
+      </c>
+      <c r="AC101" s="74">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="AD101" s="72">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="AE101" s="73">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="AF101" s="74">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="AG101" s="72">
+        <v>0.621</v>
+      </c>
+      <c r="AH101" s="73">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="AI101" s="74">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="AJ101" s="78"/>
+      <c r="AK101" s="78"/>
+      <c r="AL101" s="78"/>
       <c r="AM101" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AN101" s="76">
-        <v>0.28100000000000003</v>
-      </c>
-      <c r="AO101" s="77">
-        <v>0.39</v>
-      </c>
-      <c r="AP101" s="78">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="AQ101" s="76">
-        <v>0.3</v>
-      </c>
-      <c r="AR101" s="77">
-        <v>0.33200000000000002</v>
-      </c>
-      <c r="AS101" s="78">
-        <v>0.318</v>
-      </c>
-      <c r="AT101" s="76">
-        <v>0.315</v>
-      </c>
-      <c r="AU101" s="77">
-        <v>0.31</v>
-      </c>
-      <c r="AV101" s="78">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="AW101" s="71"/>
-      <c r="AX101" s="71"/>
-      <c r="AY101" s="71"/>
-      <c r="AZ101" s="71"/>
+      <c r="AN101" s="72">
+        <v>0.434</v>
+      </c>
+      <c r="AO101" s="73">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="AP101" s="74">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="AQ101" s="72">
+        <v>0.373</v>
+      </c>
+      <c r="AR101" s="73">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="AS101" s="74">
+        <v>0.372</v>
+      </c>
+      <c r="AT101" s="72">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="AU101" s="73">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="AV101" s="74">
+        <v>0.379</v>
+      </c>
+      <c r="AW101" s="67"/>
+      <c r="AX101" s="67"/>
+      <c r="AY101" s="67"/>
+      <c r="AZ101" s="67"/>
       <c r="BA101" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="BB101" s="76">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="BC101" s="77">
-        <v>0.191</v>
-      </c>
-      <c r="BD101" s="78">
-        <v>0.115</v>
-      </c>
-      <c r="BE101" s="76">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="BF101" s="77">
-        <v>0.191</v>
-      </c>
-      <c r="BG101" s="78">
-        <v>0.186</v>
-      </c>
-      <c r="BH101" s="76">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="BI101" s="77">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="BJ101" s="78">
-        <v>0.23699999999999999</v>
+      <c r="BB101" s="72">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="BC101" s="73">
+        <v>0.106</v>
+      </c>
+      <c r="BD101" s="74">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="BE101" s="72">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="BF101" s="73">
+        <v>0.23</v>
+      </c>
+      <c r="BG101" s="74">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="BH101" s="72">
+        <v>0.248</v>
+      </c>
+      <c r="BI101" s="73">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="BJ101" s="74">
+        <v>0.23400000000000001</v>
       </c>
       <c r="BO101" s="48" t="s">
         <v>24</v>
       </c>
       <c r="BP101" s="62">
-        <v>0.91800000000000004</v>
+        <v>0.94</v>
       </c>
       <c r="BQ101" s="43">
-        <v>0.48299999999999998</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="BR101" s="54">
-        <v>0.439</v>
+        <v>0.67</v>
       </c>
       <c r="BS101" s="62">
-        <v>0.89700000000000002</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="BT101" s="43">
-        <v>0.61699999999999999</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="BU101" s="54">
-        <v>0.36699999999999999</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="BV101" s="62">
-        <v>0.70499999999999996</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="BW101" s="43">
-        <v>0.49</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="BX101" s="54">
-        <v>0.30299999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="BY101" s="45"/>
       <c r="BZ101" s="45"/>
@@ -5743,31 +5731,31 @@
         <v>24</v>
       </c>
       <c r="CE101" s="62">
-        <v>0.54700000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="CF101" s="43">
-        <v>0.32</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="CG101" s="54">
-        <v>0.221</v>
+        <v>0.222</v>
       </c>
       <c r="CH101" s="62">
-        <v>0.36199999999999999</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="CI101" s="43">
-        <v>0.23699999999999999</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="CJ101" s="54">
-        <v>0.14499999999999999</v>
+        <v>0.157</v>
       </c>
       <c r="CK101" s="59">
-        <v>0.41899999999999998</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="CL101" s="43">
-        <v>0.214</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="CM101" s="54">
-        <v>0.128</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="CN101" s="42"/>
       <c r="CO101" s="42"/>
@@ -5777,31 +5765,31 @@
         <v>24</v>
       </c>
       <c r="CS101" s="62">
-        <v>0.30199999999999999</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="CT101" s="43">
-        <v>0.214</v>
+        <v>7.8E-2</v>
       </c>
       <c r="CU101" s="54">
-        <v>9.7000000000000003E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="CV101" s="62">
-        <v>0.26100000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="CW101" s="43">
-        <v>0.13700000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="CX101" s="54">
-        <v>0.113</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="CY101" s="59">
-        <v>0.21099999999999999</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="CZ101" s="43">
-        <v>0.11799999999999999</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="DA101" s="54">
-        <v>0.108</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="DB101" s="42"/>
       <c r="DC101" s="42"/>
@@ -5815,31 +5803,31 @@
         <v>24</v>
       </c>
       <c r="DK101" s="62">
-        <v>0.874</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="DL101" s="43">
-        <v>0.57499999999999996</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="DM101" s="54">
-        <v>0.377</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="DN101" s="62">
-        <v>0.85699999999999998</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="DO101" s="43">
-        <v>0.62</v>
+        <v>0.65700000000000003</v>
       </c>
       <c r="DP101" s="54">
-        <v>0.375</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="DQ101" s="59">
-        <v>0.81599999999999995</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="DR101" s="43">
-        <v>0.53500000000000003</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="DS101" s="54">
-        <v>0.38500000000000001</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="DT101" s="42"/>
       <c r="DU101" s="42"/>
@@ -5849,31 +5837,31 @@
         <v>24</v>
       </c>
       <c r="DY101" s="62">
-        <v>0.57399999999999995</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="DZ101" s="43">
-        <v>0.39</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="EA101" s="54">
-        <v>0.23799999999999999</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="EB101" s="62">
-        <v>0.46100000000000002</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="EC101" s="43">
-        <v>0.33200000000000002</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="ED101" s="54">
-        <v>0.21199999999999999</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="EE101" s="59">
-        <v>0.54200000000000004</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="EF101" s="43">
-        <v>0.31</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="EG101" s="54">
-        <v>0.22800000000000001</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="EH101" s="42"/>
       <c r="EI101" s="42"/>
@@ -5882,37 +5870,37 @@
         <v>24</v>
       </c>
       <c r="EL101" s="62">
-        <v>0.34899999999999998</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="EM101" s="43">
-        <v>0.191</v>
+        <v>0.106</v>
       </c>
       <c r="EN101" s="54">
-        <v>0.125</v>
+        <v>0.155</v>
       </c>
       <c r="EO101" s="62">
-        <v>0.32700000000000001</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="EP101" s="43">
-        <v>0.191</v>
+        <v>0.23</v>
       </c>
       <c r="EQ101" s="54">
-        <v>0.127</v>
+        <v>0.15</v>
       </c>
       <c r="ER101" s="59">
-        <v>0.316</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="ES101" s="43">
-        <v>0.20499999999999999</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="ET101" s="54">
-        <v>0.16300000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="EU101" s="42"/>
       <c r="EV101" s="42"/>
       <c r="EW101" s="42"/>
     </row>
-    <row r="102" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="102" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M102" s="4" t="s">
         <v>25</v>
       </c>
@@ -5946,98 +5934,98 @@
       <c r="Z102" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA102" s="79">
+      <c r="AA102" s="75">
         <v>0.83499999999999996</v>
       </c>
-      <c r="AB102" s="80">
+      <c r="AB102" s="76">
         <v>0.82699999999999996</v>
       </c>
-      <c r="AC102" s="72">
+      <c r="AC102" s="68">
         <v>0.85</v>
       </c>
-      <c r="AD102" s="79">
+      <c r="AD102" s="75">
         <v>0.72099999999999997</v>
       </c>
-      <c r="AE102" s="80">
+      <c r="AE102" s="76">
         <v>0.67800000000000005</v>
       </c>
-      <c r="AF102" s="72">
+      <c r="AF102" s="68">
         <v>0.69299999999999995</v>
       </c>
-      <c r="AG102" s="79">
+      <c r="AG102" s="75">
         <v>0.60099999999999998</v>
       </c>
-      <c r="AH102" s="80">
+      <c r="AH102" s="76">
         <v>0.64700000000000002</v>
       </c>
-      <c r="AI102" s="72">
+      <c r="AI102" s="68">
         <v>0.61199999999999999</v>
       </c>
-      <c r="AJ102" s="82"/>
-      <c r="AK102" s="82"/>
-      <c r="AL102" s="82"/>
+      <c r="AJ102" s="78"/>
+      <c r="AK102" s="78"/>
+      <c r="AL102" s="78"/>
       <c r="AM102" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="AN102" s="79">
+      <c r="AN102" s="75">
         <v>0.48499999999999999</v>
       </c>
-      <c r="AO102" s="80">
+      <c r="AO102" s="76">
         <v>0.48199999999999998</v>
       </c>
-      <c r="AP102" s="72">
+      <c r="AP102" s="68">
         <v>0.45800000000000002</v>
       </c>
-      <c r="AQ102" s="79">
+      <c r="AQ102" s="75">
         <v>0.44700000000000001</v>
       </c>
-      <c r="AR102" s="80">
+      <c r="AR102" s="76">
         <v>0.41199999999999998</v>
       </c>
-      <c r="AS102" s="72">
+      <c r="AS102" s="68">
         <v>0.40400000000000003</v>
       </c>
-      <c r="AT102" s="79">
+      <c r="AT102" s="75">
         <v>0.42399999999999999</v>
       </c>
-      <c r="AU102" s="80">
+      <c r="AU102" s="76">
         <v>0.43</v>
       </c>
-      <c r="AV102" s="72">
+      <c r="AV102" s="68">
         <v>0.376</v>
       </c>
-      <c r="AW102" s="71"/>
-      <c r="AX102" s="71"/>
-      <c r="AY102" s="71"/>
-      <c r="AZ102" s="71"/>
+      <c r="AW102" s="67"/>
+      <c r="AX102" s="67"/>
+      <c r="AY102" s="67"/>
+      <c r="AZ102" s="67"/>
       <c r="BA102" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="BB102" s="79">
+      <c r="BB102" s="75">
         <v>0.29199999999999998</v>
       </c>
-      <c r="BC102" s="80">
+      <c r="BC102" s="76">
         <v>0.28599999999999998</v>
       </c>
-      <c r="BD102" s="72">
+      <c r="BD102" s="68">
         <v>0.30399999999999999</v>
       </c>
-      <c r="BE102" s="79">
+      <c r="BE102" s="75">
         <v>0.26500000000000001</v>
       </c>
-      <c r="BF102" s="80">
+      <c r="BF102" s="76">
         <v>0.245</v>
       </c>
-      <c r="BG102" s="72">
+      <c r="BG102" s="68">
         <v>0.253</v>
       </c>
-      <c r="BH102" s="79">
+      <c r="BH102" s="75">
         <v>0.26900000000000002</v>
       </c>
-      <c r="BI102" s="80">
+      <c r="BI102" s="76">
         <v>0.28100000000000003</v>
       </c>
-      <c r="BJ102" s="72">
+      <c r="BJ102" s="68">
         <v>0.25900000000000001</v>
       </c>
       <c r="BO102" s="49" t="s">
@@ -6248,7 +6236,7 @@
       <c r="EV102" s="42"/>
       <c r="EW102" s="42"/>
     </row>
-    <row r="103" spans="13:153" ht="24.9" customHeight="1">
+    <row r="103" spans="13:153" ht="24.95" customHeight="1">
       <c r="M103" s="13" t="s">
         <v>10</v>
       </c>
@@ -6282,98 +6270,98 @@
       <c r="Z103" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AA103" s="73">
+      <c r="AA103" s="69">
         <v>0.85099999999999998</v>
       </c>
-      <c r="AB103" s="74">
+      <c r="AB103" s="70">
         <v>0.874</v>
       </c>
-      <c r="AC103" s="75">
+      <c r="AC103" s="71">
         <v>0.57899999999999996</v>
       </c>
-      <c r="AD103" s="73">
+      <c r="AD103" s="69">
         <v>0.72099999999999997</v>
       </c>
-      <c r="AE103" s="74">
+      <c r="AE103" s="70">
         <v>0.63</v>
       </c>
-      <c r="AF103" s="75">
+      <c r="AF103" s="71">
         <v>0.77100000000000002</v>
       </c>
-      <c r="AG103" s="73">
+      <c r="AG103" s="69">
         <v>0.53200000000000003</v>
       </c>
-      <c r="AH103" s="74">
+      <c r="AH103" s="70">
         <v>0.56299999999999994</v>
       </c>
-      <c r="AI103" s="75">
+      <c r="AI103" s="71">
         <v>0.60599999999999998</v>
       </c>
-      <c r="AJ103" s="82"/>
-      <c r="AK103" s="82"/>
-      <c r="AL103" s="82"/>
+      <c r="AJ103" s="78"/>
+      <c r="AK103" s="78"/>
+      <c r="AL103" s="78"/>
       <c r="AM103" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="AN103" s="73">
+      <c r="AN103" s="69">
         <v>0.47599999999999998</v>
       </c>
-      <c r="AO103" s="74">
+      <c r="AO103" s="70">
         <v>0.432</v>
       </c>
-      <c r="AP103" s="75">
+      <c r="AP103" s="71">
         <v>0.48399999999999999</v>
       </c>
-      <c r="AQ103" s="73">
+      <c r="AQ103" s="69">
         <v>0.40100000000000002</v>
       </c>
-      <c r="AR103" s="74">
+      <c r="AR103" s="70">
         <v>0.42799999999999999</v>
       </c>
-      <c r="AS103" s="75">
+      <c r="AS103" s="71">
         <v>0.41899999999999998</v>
       </c>
-      <c r="AT103" s="73">
+      <c r="AT103" s="69">
         <v>0.39200000000000002</v>
       </c>
-      <c r="AU103" s="74">
+      <c r="AU103" s="70">
         <v>0.41499999999999998</v>
       </c>
-      <c r="AV103" s="75">
+      <c r="AV103" s="71">
         <v>0.378</v>
       </c>
-      <c r="AW103" s="71"/>
-      <c r="AX103" s="71"/>
-      <c r="AY103" s="71"/>
-      <c r="AZ103" s="71"/>
+      <c r="AW103" s="67"/>
+      <c r="AX103" s="67"/>
+      <c r="AY103" s="67"/>
+      <c r="AZ103" s="67"/>
       <c r="BA103" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="BB103" s="73">
+      <c r="BB103" s="69">
         <v>0.33600000000000002</v>
       </c>
-      <c r="BC103" s="74">
+      <c r="BC103" s="70">
         <v>0.29699999999999999</v>
       </c>
-      <c r="BD103" s="75">
+      <c r="BD103" s="71">
         <v>0.21299999999999999</v>
       </c>
-      <c r="BE103" s="73">
+      <c r="BE103" s="69">
         <v>0.20799999999999999</v>
       </c>
-      <c r="BF103" s="74">
+      <c r="BF103" s="70">
         <v>0.25</v>
       </c>
-      <c r="BG103" s="75">
+      <c r="BG103" s="71">
         <v>0.20599999999999999</v>
       </c>
-      <c r="BH103" s="73">
+      <c r="BH103" s="69">
         <v>0.23100000000000001</v>
       </c>
-      <c r="BI103" s="74">
+      <c r="BI103" s="70">
         <v>0.193</v>
       </c>
-      <c r="BJ103" s="75">
+      <c r="BJ103" s="71">
         <v>0.27</v>
       </c>
       <c r="BO103" s="47" t="s">
@@ -6584,7 +6572,7 @@
       <c r="EV103" s="42"/>
       <c r="EW103" s="42"/>
     </row>
-    <row r="104" spans="13:153" ht="24.9" customHeight="1">
+    <row r="104" spans="13:153" ht="24.95" customHeight="1">
       <c r="M104" s="3" t="s">
         <v>17</v>
       </c>
@@ -6618,98 +6606,98 @@
       <c r="Z104" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA104" s="76">
+      <c r="AA104" s="72">
         <v>0.84099999999999997</v>
       </c>
-      <c r="AB104" s="77">
+      <c r="AB104" s="73">
         <v>0.83199999999999996</v>
       </c>
-      <c r="AC104" s="78">
+      <c r="AC104" s="74">
         <v>0.85199999999999998</v>
       </c>
-      <c r="AD104" s="76">
+      <c r="AD104" s="72">
         <v>0.69299999999999995</v>
       </c>
-      <c r="AE104" s="77">
+      <c r="AE104" s="73">
         <v>0.61699999999999999</v>
       </c>
-      <c r="AF104" s="78">
+      <c r="AF104" s="74">
         <v>0.72699999999999998</v>
       </c>
-      <c r="AG104" s="76">
+      <c r="AG104" s="72">
         <v>0.623</v>
       </c>
-      <c r="AH104" s="77">
+      <c r="AH104" s="73">
         <v>0.59599999999999997</v>
       </c>
-      <c r="AI104" s="78">
+      <c r="AI104" s="74">
         <v>0.63700000000000001</v>
       </c>
-      <c r="AJ104" s="82"/>
-      <c r="AK104" s="82"/>
-      <c r="AL104" s="82"/>
+      <c r="AJ104" s="78"/>
+      <c r="AK104" s="78"/>
+      <c r="AL104" s="78"/>
       <c r="AM104" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AN104" s="76">
+      <c r="AN104" s="72">
         <v>0.52300000000000002</v>
       </c>
-      <c r="AO104" s="77">
+      <c r="AO104" s="73">
         <v>0.439</v>
       </c>
-      <c r="AP104" s="78">
+      <c r="AP104" s="74">
         <v>0.441</v>
       </c>
-      <c r="AQ104" s="76">
+      <c r="AQ104" s="72">
         <v>0.379</v>
       </c>
-      <c r="AR104" s="77">
+      <c r="AR104" s="73">
         <v>0.375</v>
       </c>
-      <c r="AS104" s="78">
+      <c r="AS104" s="74">
         <v>0.34599999999999997</v>
       </c>
-      <c r="AT104" s="76">
+      <c r="AT104" s="72">
         <v>0.35699999999999998</v>
       </c>
-      <c r="AU104" s="77">
+      <c r="AU104" s="73">
         <v>0.378</v>
       </c>
-      <c r="AV104" s="78">
+      <c r="AV104" s="74">
         <v>0.34300000000000003</v>
       </c>
-      <c r="AW104" s="71"/>
-      <c r="AX104" s="71"/>
-      <c r="AY104" s="71"/>
-      <c r="AZ104" s="71"/>
+      <c r="AW104" s="67"/>
+      <c r="AX104" s="67"/>
+      <c r="AY104" s="67"/>
+      <c r="AZ104" s="67"/>
       <c r="BA104" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="BB104" s="76">
+      <c r="BB104" s="72">
         <v>0.16600000000000001</v>
       </c>
-      <c r="BC104" s="77">
+      <c r="BC104" s="73">
         <v>0.26600000000000001</v>
       </c>
-      <c r="BD104" s="78">
+      <c r="BD104" s="74">
         <v>0.24199999999999999</v>
       </c>
-      <c r="BE104" s="76">
+      <c r="BE104" s="72">
         <v>0.224</v>
       </c>
-      <c r="BF104" s="77">
+      <c r="BF104" s="73">
         <v>0.20499999999999999</v>
       </c>
-      <c r="BG104" s="78">
+      <c r="BG104" s="74">
         <v>0.21</v>
       </c>
-      <c r="BH104" s="76">
+      <c r="BH104" s="72">
         <v>0.252</v>
       </c>
-      <c r="BI104" s="77">
+      <c r="BI104" s="73">
         <v>0.246</v>
       </c>
-      <c r="BJ104" s="78">
+      <c r="BJ104" s="74">
         <v>0.23599999999999999</v>
       </c>
       <c r="BO104" s="48" t="s">
@@ -6920,163 +6908,163 @@
       <c r="EV104" s="42"/>
       <c r="EW104" s="42"/>
     </row>
-    <row r="105" spans="13:153" ht="24.9" customHeight="1">
+    <row r="105" spans="13:153" ht="24.95" customHeight="1">
       <c r="M105" s="3" t="s">
         <v>27</v>
       </c>
       <c r="N105" s="32">
-        <v>0.123</v>
+        <v>0.112</v>
       </c>
       <c r="O105" s="33">
-        <v>0.11600000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="P105" s="34">
-        <v>0.16500000000000001</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="Q105" s="32">
-        <v>0.17699999999999999</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="R105" s="33">
-        <v>0.128</v>
+        <v>0.153</v>
       </c>
       <c r="S105" s="34">
-        <v>0.11799999999999999</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="T105" s="32">
-        <v>0.157</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="U105" s="33">
-        <v>0.17699999999999999</v>
+        <v>0.185</v>
       </c>
       <c r="V105" s="34">
-        <v>0.122</v>
+        <v>0.158</v>
       </c>
       <c r="Z105" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AA105" s="76">
-        <v>0.44400000000000001</v>
-      </c>
-      <c r="AB105" s="77">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="AC105" s="78">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="AD105" s="76">
-        <v>0.52600000000000002</v>
-      </c>
-      <c r="AE105" s="77">
-        <v>0.57799999999999996</v>
-      </c>
-      <c r="AF105" s="78">
-        <v>0.54400000000000004</v>
-      </c>
-      <c r="AG105" s="76">
-        <v>0.54700000000000004</v>
-      </c>
-      <c r="AH105" s="77">
-        <v>0.51200000000000001</v>
-      </c>
-      <c r="AI105" s="78">
-        <v>0.56799999999999995</v>
-      </c>
-      <c r="AJ105" s="82"/>
-      <c r="AK105" s="82"/>
-      <c r="AL105" s="82"/>
+      <c r="AA105" s="72">
+        <v>0.501</v>
+      </c>
+      <c r="AB105" s="73">
+        <v>0.751</v>
+      </c>
+      <c r="AC105" s="74">
+        <v>0.80300000000000005</v>
+      </c>
+      <c r="AD105" s="72">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="AE105" s="73">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="AF105" s="74">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="AG105" s="72">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="AH105" s="73">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="AI105" s="74">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="AJ105" s="78"/>
+      <c r="AK105" s="78"/>
+      <c r="AL105" s="78"/>
       <c r="AM105" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="AN105" s="76">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="AO105" s="77">
+      <c r="AN105" s="72">
+        <v>0.318</v>
+      </c>
+      <c r="AO105" s="73">
+        <v>0.36</v>
+      </c>
+      <c r="AP105" s="74">
+        <v>0.442</v>
+      </c>
+      <c r="AQ105" s="72">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="AR105" s="73">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="AS105" s="74">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="AT105" s="72">
         <v>0.38100000000000001</v>
       </c>
-      <c r="AP105" s="78">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="AQ105" s="76">
-        <v>0.23799999999999999</v>
-      </c>
-      <c r="AR105" s="77">
-        <v>0.27</v>
-      </c>
-      <c r="AS105" s="78">
-        <v>0.31900000000000001</v>
-      </c>
-      <c r="AT105" s="76">
-        <v>0.29599999999999999</v>
-      </c>
-      <c r="AU105" s="77">
-        <v>0.25700000000000001</v>
-      </c>
-      <c r="AV105" s="78">
-        <v>0.36</v>
-      </c>
-      <c r="AW105" s="71"/>
-      <c r="AX105" s="71"/>
-      <c r="AY105" s="71"/>
-      <c r="AZ105" s="71"/>
+      <c r="AU105" s="73">
+        <v>0.374</v>
+      </c>
+      <c r="AV105" s="74">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="AW105" s="67"/>
+      <c r="AX105" s="67"/>
+      <c r="AY105" s="67"/>
+      <c r="AZ105" s="67"/>
       <c r="BA105" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="BB105" s="76">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="BC105" s="77">
-        <v>0.113</v>
-      </c>
-      <c r="BD105" s="78">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="BE105" s="76">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="BF105" s="77">
-        <v>0.192</v>
-      </c>
-      <c r="BG105" s="78">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="BH105" s="76">
+      <c r="BB105" s="72">
+        <v>0.15</v>
+      </c>
+      <c r="BC105" s="73">
+        <v>0.251</v>
+      </c>
+      <c r="BD105" s="74">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="BE105" s="72">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="BF105" s="73">
         <v>0.22700000000000001</v>
       </c>
-      <c r="BI105" s="77">
-        <v>0.23200000000000001</v>
-      </c>
-      <c r="BJ105" s="78">
-        <v>0.215</v>
+      <c r="BG105" s="74">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="BH105" s="72">
+        <v>0.247</v>
+      </c>
+      <c r="BI105" s="73">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="BJ105" s="74">
+        <v>0.24</v>
       </c>
       <c r="BO105" s="48" t="s">
         <v>27</v>
       </c>
       <c r="BP105" s="62">
-        <v>0.94799999999999995</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="BQ105" s="43">
-        <v>0.56999999999999995</v>
+        <v>0.82</v>
       </c>
       <c r="BR105" s="54">
-        <v>0.48199999999999998</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="BS105" s="62">
-        <v>0.94899999999999995</v>
+        <v>0.69899999999999995</v>
       </c>
       <c r="BT105" s="43">
-        <v>0.5</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="BU105" s="54">
-        <v>0.38300000000000001</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="BV105" s="62">
-        <v>0.65600000000000003</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="BW105" s="43">
-        <v>0.41099999999999998</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="BX105" s="54">
-        <v>0.311</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="BY105" s="45"/>
       <c r="BZ105" s="45"/>
@@ -7087,31 +7075,31 @@
         <v>27</v>
       </c>
       <c r="CE105" s="62">
-        <v>0.375</v>
+        <v>0.44</v>
       </c>
       <c r="CF105" s="43">
-        <v>0.32600000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="CG105" s="54">
-        <v>1.7000000000000001E-2</v>
+        <v>0.253</v>
       </c>
       <c r="CH105" s="62">
-        <v>0.29699999999999999</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="CI105" s="43">
-        <v>0.187</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="CJ105" s="54">
-        <v>0.1</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="CK105" s="59">
-        <v>0.42699999999999999</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="CL105" s="43">
-        <v>0.13800000000000001</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="CM105" s="54">
-        <v>0.152</v>
+        <v>0.157</v>
       </c>
       <c r="CN105" s="42"/>
       <c r="CO105" s="42"/>
@@ -7121,28 +7109,28 @@
         <v>27</v>
       </c>
       <c r="CS105" s="62">
-        <v>0.23699999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="CT105" s="43">
-        <v>0.11600000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="CU105" s="54">
-        <v>0.104</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="CV105" s="62">
-        <v>0.19500000000000001</v>
+        <v>0.253</v>
       </c>
       <c r="CW105" s="43">
-        <v>0.128</v>
+        <v>0.153</v>
       </c>
       <c r="CX105" s="54">
-        <v>7.9000000000000001E-2</v>
+        <v>0.108</v>
       </c>
       <c r="CY105" s="59">
-        <v>0.187</v>
+        <v>0.219</v>
       </c>
       <c r="CZ105" s="43">
-        <v>0.17699999999999999</v>
+        <v>0.185</v>
       </c>
       <c r="DA105" s="54">
         <v>0.106</v>
@@ -7159,31 +7147,31 @@
         <v>27</v>
       </c>
       <c r="DK105" s="62">
-        <v>0.90600000000000003</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="DL105" s="43">
-        <v>0.45500000000000002</v>
+        <v>0.751</v>
       </c>
       <c r="DM105" s="54">
-        <v>0.39600000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="DN105" s="62">
-        <v>0.91300000000000003</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="DO105" s="43">
-        <v>0.57799999999999996</v>
+        <v>0.66200000000000003</v>
       </c>
       <c r="DP105" s="54">
-        <v>0.42899999999999999</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="DQ105" s="59">
-        <v>0.74399999999999999</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="DR105" s="43">
-        <v>0.51200000000000001</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="DS105" s="54">
-        <v>0.39300000000000002</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="DT105" s="42"/>
       <c r="DU105" s="42"/>
@@ -7193,31 +7181,31 @@
         <v>27</v>
       </c>
       <c r="DY105" s="62">
-        <v>0.52</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="DZ105" s="43">
-        <v>0.38100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="EA105" s="54">
-        <v>0.11899999999999999</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="EB105" s="62">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="EC105" s="43">
-        <v>0.27</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="ED105" s="54">
-        <v>0.159</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="EE105" s="59">
-        <v>0.55500000000000005</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="EF105" s="43">
-        <v>0.25700000000000001</v>
+        <v>0.374</v>
       </c>
       <c r="EG105" s="54">
-        <v>0.23899999999999999</v>
+        <v>0.254</v>
       </c>
       <c r="EH105" s="42"/>
       <c r="EI105" s="42"/>
@@ -7226,37 +7214,37 @@
         <v>27</v>
       </c>
       <c r="EL105" s="62">
-        <v>0.30599999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="EM105" s="43">
-        <v>0.113</v>
+        <v>0.251</v>
       </c>
       <c r="EN105" s="54">
-        <v>0.127</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="EO105" s="62">
-        <v>0.29499999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="EP105" s="43">
-        <v>0.192</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="EQ105" s="54">
-        <v>0.125</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="ER105" s="59">
-        <v>0.30499999999999999</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="ES105" s="43">
-        <v>0.23200000000000001</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="ET105" s="54">
-        <v>0.16600000000000001</v>
+        <v>0.184</v>
       </c>
       <c r="EU105" s="42"/>
       <c r="EV105" s="42"/>
       <c r="EW105" s="42"/>
     </row>
-    <row r="106" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="106" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M106" s="4" t="s">
         <v>26</v>
       </c>
@@ -7290,98 +7278,98 @@
       <c r="Z106" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AA106" s="79">
+      <c r="AA106" s="75">
         <v>0.82599999999999996</v>
       </c>
-      <c r="AB106" s="80">
+      <c r="AB106" s="76">
         <v>0.83399999999999996</v>
       </c>
-      <c r="AC106" s="72">
+      <c r="AC106" s="68">
         <v>0.86199999999999999</v>
       </c>
-      <c r="AD106" s="79">
+      <c r="AD106" s="75">
         <v>0.66900000000000004</v>
       </c>
-      <c r="AE106" s="80">
+      <c r="AE106" s="76">
         <v>0.76300000000000001</v>
       </c>
-      <c r="AF106" s="72">
+      <c r="AF106" s="68">
         <v>0.66700000000000004</v>
       </c>
-      <c r="AG106" s="79">
+      <c r="AG106" s="75">
         <v>0.66600000000000004</v>
       </c>
-      <c r="AH106" s="80">
+      <c r="AH106" s="76">
         <v>0.67900000000000005</v>
       </c>
-      <c r="AI106" s="72">
+      <c r="AI106" s="68">
         <v>0.63200000000000001</v>
       </c>
-      <c r="AJ106" s="82"/>
-      <c r="AK106" s="82"/>
-      <c r="AL106" s="82"/>
+      <c r="AJ106" s="78"/>
+      <c r="AK106" s="78"/>
+      <c r="AL106" s="78"/>
       <c r="AM106" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="AN106" s="79">
+      <c r="AN106" s="75">
         <v>0.46899999999999997</v>
       </c>
-      <c r="AO106" s="80">
+      <c r="AO106" s="76">
         <v>0.46899999999999997</v>
       </c>
-      <c r="AP106" s="72">
+      <c r="AP106" s="68">
         <v>0.45900000000000002</v>
       </c>
-      <c r="AQ106" s="79">
+      <c r="AQ106" s="75">
         <v>0.41099999999999998</v>
       </c>
-      <c r="AR106" s="80">
+      <c r="AR106" s="76">
         <v>0.43</v>
       </c>
-      <c r="AS106" s="72">
+      <c r="AS106" s="68">
         <v>0.48</v>
       </c>
-      <c r="AT106" s="79">
+      <c r="AT106" s="75">
         <v>0.45200000000000001</v>
       </c>
-      <c r="AU106" s="80">
+      <c r="AU106" s="76">
         <v>0.41</v>
       </c>
-      <c r="AV106" s="72">
+      <c r="AV106" s="68">
         <v>0.38600000000000001</v>
       </c>
-      <c r="AW106" s="71"/>
-      <c r="AX106" s="71"/>
-      <c r="AY106" s="71"/>
-      <c r="AZ106" s="71"/>
+      <c r="AW106" s="67"/>
+      <c r="AX106" s="67"/>
+      <c r="AY106" s="67"/>
+      <c r="AZ106" s="67"/>
       <c r="BA106" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="BB106" s="79">
+      <c r="BB106" s="75">
         <v>0.32600000000000001</v>
       </c>
-      <c r="BC106" s="80">
+      <c r="BC106" s="76">
         <v>0.32600000000000001</v>
       </c>
-      <c r="BD106" s="72">
+      <c r="BD106" s="68">
         <v>0.36599999999999999</v>
       </c>
-      <c r="BE106" s="79">
+      <c r="BE106" s="75">
         <v>0.27300000000000002</v>
       </c>
-      <c r="BF106" s="80">
+      <c r="BF106" s="76">
         <v>0.24399999999999999</v>
       </c>
-      <c r="BG106" s="72">
+      <c r="BG106" s="68">
         <v>0.217</v>
       </c>
-      <c r="BH106" s="79">
+      <c r="BH106" s="75">
         <v>0.25</v>
       </c>
-      <c r="BI106" s="80">
+      <c r="BI106" s="76">
         <v>0.26</v>
       </c>
-      <c r="BJ106" s="72">
+      <c r="BJ106" s="68">
         <v>0.245</v>
       </c>
       <c r="BO106" s="49" t="s">
@@ -7592,7 +7580,7 @@
       <c r="EV106" s="42"/>
       <c r="EW106" s="42"/>
     </row>
-    <row r="107" spans="13:153" ht="24.9" customHeight="1">
+    <row r="107" spans="13:153" ht="24.95" customHeight="1">
       <c r="M107" s="13" t="s">
         <v>11</v>
       </c>
@@ -7626,98 +7614,98 @@
       <c r="Z107" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="AA107" s="73">
+      <c r="AA107" s="69">
         <v>0.6</v>
       </c>
-      <c r="AB107" s="74">
+      <c r="AB107" s="70">
         <v>0.505</v>
       </c>
-      <c r="AC107" s="75">
+      <c r="AC107" s="71">
         <v>0.63700000000000001</v>
       </c>
-      <c r="AD107" s="73">
+      <c r="AD107" s="69">
         <v>0.56000000000000005</v>
       </c>
-      <c r="AE107" s="74">
+      <c r="AE107" s="70">
         <v>0.57099999999999995</v>
       </c>
-      <c r="AF107" s="75">
+      <c r="AF107" s="71">
         <v>0.54300000000000004</v>
       </c>
-      <c r="AG107" s="73">
+      <c r="AG107" s="69">
         <v>0.52700000000000002</v>
       </c>
-      <c r="AH107" s="74">
+      <c r="AH107" s="70">
         <v>0.504</v>
       </c>
-      <c r="AI107" s="75">
+      <c r="AI107" s="71">
         <v>0.45600000000000002</v>
       </c>
-      <c r="AJ107" s="82"/>
-      <c r="AK107" s="82"/>
-      <c r="AL107" s="82"/>
+      <c r="AJ107" s="78"/>
+      <c r="AK107" s="78"/>
+      <c r="AL107" s="78"/>
       <c r="AM107" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AN107" s="73">
+      <c r="AN107" s="69">
         <v>0.42699999999999999</v>
       </c>
-      <c r="AO107" s="74">
+      <c r="AO107" s="70">
         <v>0.42299999999999999</v>
       </c>
-      <c r="AP107" s="75">
+      <c r="AP107" s="71">
         <v>0.41699999999999998</v>
       </c>
-      <c r="AQ107" s="73">
+      <c r="AQ107" s="69">
         <v>0.37</v>
       </c>
-      <c r="AR107" s="74">
+      <c r="AR107" s="70">
         <v>0.39300000000000002</v>
       </c>
-      <c r="AS107" s="75">
+      <c r="AS107" s="71">
         <v>0.39100000000000001</v>
       </c>
-      <c r="AT107" s="73">
+      <c r="AT107" s="69">
         <v>0.36</v>
       </c>
-      <c r="AU107" s="74">
+      <c r="AU107" s="70">
         <v>0.374</v>
       </c>
-      <c r="AV107" s="75">
+      <c r="AV107" s="71">
         <v>0.34399999999999997</v>
       </c>
-      <c r="AW107" s="71"/>
-      <c r="AX107" s="71"/>
-      <c r="AY107" s="71"/>
-      <c r="AZ107" s="71"/>
+      <c r="AW107" s="67"/>
+      <c r="AX107" s="67"/>
+      <c r="AY107" s="67"/>
+      <c r="AZ107" s="67"/>
       <c r="BA107" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="BB107" s="73">
+      <c r="BB107" s="69">
         <v>0.33500000000000002</v>
       </c>
-      <c r="BC107" s="74">
+      <c r="BC107" s="70">
         <v>0.34</v>
       </c>
-      <c r="BD107" s="75">
+      <c r="BD107" s="71">
         <v>0.27200000000000002</v>
       </c>
-      <c r="BE107" s="73">
+      <c r="BE107" s="69">
         <v>0.26700000000000002</v>
       </c>
-      <c r="BF107" s="74">
+      <c r="BF107" s="70">
         <v>0.23799999999999999</v>
       </c>
-      <c r="BG107" s="75">
+      <c r="BG107" s="71">
         <v>0.26100000000000001</v>
       </c>
-      <c r="BH107" s="73">
+      <c r="BH107" s="69">
         <v>0.26800000000000002</v>
       </c>
-      <c r="BI107" s="74">
+      <c r="BI107" s="70">
         <v>0.26500000000000001</v>
       </c>
-      <c r="BJ107" s="75">
+      <c r="BJ107" s="71">
         <v>0.253</v>
       </c>
       <c r="BO107" s="47" t="s">
@@ -7928,7 +7916,7 @@
       <c r="EV107" s="42"/>
       <c r="EW107" s="42"/>
     </row>
-    <row r="108" spans="13:153" ht="24.9" customHeight="1">
+    <row r="108" spans="13:153" ht="24.95" customHeight="1">
       <c r="M108" s="3" t="s">
         <v>18</v>
       </c>
@@ -7962,98 +7950,98 @@
       <c r="Z108" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AA108" s="76">
+      <c r="AA108" s="72">
         <v>0.82699999999999996</v>
       </c>
-      <c r="AB108" s="77">
+      <c r="AB108" s="73">
         <v>0.82699999999999996</v>
       </c>
-      <c r="AC108" s="78">
+      <c r="AC108" s="74">
         <v>0.80800000000000005</v>
       </c>
-      <c r="AD108" s="76">
+      <c r="AD108" s="72">
         <v>0.745</v>
       </c>
-      <c r="AE108" s="77">
+      <c r="AE108" s="73">
         <v>0.623</v>
       </c>
-      <c r="AF108" s="78">
+      <c r="AF108" s="74">
         <v>0.60599999999999998</v>
       </c>
-      <c r="AG108" s="76">
+      <c r="AG108" s="72">
         <v>0.68400000000000005</v>
       </c>
-      <c r="AH108" s="77">
+      <c r="AH108" s="73">
         <v>0.66200000000000003</v>
       </c>
-      <c r="AI108" s="78">
+      <c r="AI108" s="74">
         <v>0.61799999999999999</v>
       </c>
-      <c r="AJ108" s="82"/>
-      <c r="AK108" s="82"/>
-      <c r="AL108" s="82"/>
+      <c r="AJ108" s="78"/>
+      <c r="AK108" s="78"/>
+      <c r="AL108" s="78"/>
       <c r="AM108" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="AN108" s="76">
+      <c r="AN108" s="72">
         <v>0.51800000000000002</v>
       </c>
-      <c r="AO108" s="77">
+      <c r="AO108" s="73">
         <v>0.49099999999999999</v>
       </c>
-      <c r="AP108" s="78">
+      <c r="AP108" s="74">
         <v>0.45600000000000002</v>
       </c>
-      <c r="AQ108" s="76">
+      <c r="AQ108" s="72">
         <v>0.41</v>
       </c>
-      <c r="AR108" s="77">
+      <c r="AR108" s="73">
         <v>0.37</v>
       </c>
-      <c r="AS108" s="78">
+      <c r="AS108" s="74">
         <v>0.36199999999999999</v>
       </c>
-      <c r="AT108" s="76">
+      <c r="AT108" s="72">
         <v>0.38400000000000001</v>
       </c>
-      <c r="AU108" s="77">
+      <c r="AU108" s="73">
         <v>0.35499999999999998</v>
       </c>
-      <c r="AV108" s="78">
+      <c r="AV108" s="74">
         <v>0.35299999999999998</v>
       </c>
-      <c r="AW108" s="71"/>
-      <c r="AX108" s="71"/>
-      <c r="AY108" s="71"/>
-      <c r="AZ108" s="71"/>
+      <c r="AW108" s="67"/>
+      <c r="AX108" s="67"/>
+      <c r="AY108" s="67"/>
+      <c r="AZ108" s="67"/>
       <c r="BA108" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="BB108" s="76">
+      <c r="BB108" s="72">
         <v>0.32400000000000001</v>
       </c>
-      <c r="BC108" s="77">
+      <c r="BC108" s="73">
         <v>0.34599999999999997</v>
       </c>
-      <c r="BD108" s="78">
+      <c r="BD108" s="74">
         <v>0.29899999999999999</v>
       </c>
-      <c r="BE108" s="76">
+      <c r="BE108" s="72">
         <v>0.26300000000000001</v>
       </c>
-      <c r="BF108" s="77">
+      <c r="BF108" s="73">
         <v>0.247</v>
       </c>
-      <c r="BG108" s="78">
+      <c r="BG108" s="74">
         <v>0.22700000000000001</v>
       </c>
-      <c r="BH108" s="76">
+      <c r="BH108" s="72">
         <v>0.25900000000000001</v>
       </c>
-      <c r="BI108" s="77">
+      <c r="BI108" s="73">
         <v>0.251</v>
       </c>
-      <c r="BJ108" s="78">
+      <c r="BJ108" s="74">
         <v>0.246</v>
       </c>
       <c r="BO108" s="48" t="s">
@@ -8264,163 +8252,163 @@
       <c r="EV108" s="42"/>
       <c r="EW108" s="42"/>
     </row>
-    <row r="109" spans="13:153" ht="24.9" customHeight="1">
+    <row r="109" spans="13:153" ht="24.95" customHeight="1">
       <c r="M109" s="3" t="s">
         <v>20</v>
       </c>
       <c r="N109" s="32">
-        <v>0.25900000000000001</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="O109" s="33">
-        <v>0.21099999999999999</v>
+        <v>0.251</v>
       </c>
       <c r="P109" s="34">
-        <v>0.26400000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="Q109" s="32">
-        <v>0.23100000000000001</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="R109" s="33">
+        <v>0.192</v>
+      </c>
+      <c r="S109" s="34">
+        <v>0.151</v>
+      </c>
+      <c r="T109" s="32">
         <v>0.186</v>
       </c>
-      <c r="S109" s="34">
-        <v>0.185</v>
-      </c>
-      <c r="T109" s="32">
-        <v>0.156</v>
-      </c>
       <c r="U109" s="33">
+        <v>0.18</v>
+      </c>
+      <c r="V109" s="34">
         <v>0.16200000000000001</v>
-      </c>
-      <c r="V109" s="34">
-        <v>0.14499999999999999</v>
       </c>
       <c r="Z109" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AA109" s="76">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="AB109" s="77">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="AC109" s="78">
-        <v>0.71099999999999997</v>
-      </c>
-      <c r="AD109" s="76">
-        <v>0.58099999999999996</v>
-      </c>
-      <c r="AE109" s="77">
-        <v>0.58899999999999997</v>
-      </c>
-      <c r="AF109" s="78">
-        <v>0.627</v>
-      </c>
-      <c r="AG109" s="76">
-        <v>0.57899999999999996</v>
-      </c>
-      <c r="AH109" s="77">
-        <v>0.58799999999999997</v>
-      </c>
-      <c r="AI109" s="78">
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="AJ109" s="82"/>
-      <c r="AK109" s="82"/>
-      <c r="AL109" s="82"/>
+      <c r="AA109" s="72">
+        <v>0.77</v>
+      </c>
+      <c r="AB109" s="73">
+        <v>0.77</v>
+      </c>
+      <c r="AC109" s="74">
+        <v>0.748</v>
+      </c>
+      <c r="AD109" s="72">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="AE109" s="73">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="AF109" s="74">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="AG109" s="72">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="AH109" s="73">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="AI109" s="74">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="AJ109" s="78"/>
+      <c r="AK109" s="78"/>
+      <c r="AL109" s="78"/>
       <c r="AM109" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="AN109" s="76">
-        <v>0.28599999999999998</v>
-      </c>
-      <c r="AO109" s="77">
-        <v>0.31</v>
-      </c>
-      <c r="AP109" s="78">
-        <v>0.3</v>
-      </c>
-      <c r="AQ109" s="76">
-        <v>0.29899999999999999</v>
-      </c>
-      <c r="AR109" s="77">
-        <v>0.32400000000000001</v>
-      </c>
-      <c r="AS109" s="78">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="AT109" s="76">
-        <v>0.35</v>
-      </c>
-      <c r="AU109" s="77">
-        <v>0.35699999999999998</v>
-      </c>
-      <c r="AV109" s="78">
-        <v>0.36599999999999999</v>
-      </c>
-      <c r="AW109" s="71"/>
-      <c r="AX109" s="71"/>
-      <c r="AY109" s="71"/>
-      <c r="AZ109" s="71"/>
+      <c r="AN109" s="72">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="AO109" s="73">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="AP109" s="74">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="AQ109" s="72">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="AR109" s="73">
+        <v>0.4</v>
+      </c>
+      <c r="AS109" s="74">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="AT109" s="72">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="AU109" s="73">
+        <v>0.37</v>
+      </c>
+      <c r="AV109" s="74">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="AW109" s="67"/>
+      <c r="AX109" s="67"/>
+      <c r="AY109" s="67"/>
+      <c r="AZ109" s="67"/>
       <c r="BA109" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="BB109" s="76">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="BC109" s="77">
-        <v>0.22600000000000001</v>
-      </c>
-      <c r="BD109" s="78">
-        <v>0.28599999999999998</v>
-      </c>
-      <c r="BE109" s="76">
-        <v>0.26800000000000002</v>
-      </c>
-      <c r="BF109" s="77">
-        <v>0.23200000000000001</v>
-      </c>
-      <c r="BG109" s="78">
-        <v>0.23100000000000001</v>
-      </c>
-      <c r="BH109" s="76">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="BI109" s="77">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="BJ109" s="78">
-        <v>0.22900000000000001</v>
+      <c r="BB109" s="72">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="BC109" s="73">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="BD109" s="74">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="BE109" s="72">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="BF109" s="73">
+        <v>0.248</v>
+      </c>
+      <c r="BG109" s="74">
+        <v>0.214</v>
+      </c>
+      <c r="BH109" s="72">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="BI109" s="73">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="BJ109" s="74">
+        <v>0.247</v>
       </c>
       <c r="BO109" s="48" t="s">
         <v>20</v>
       </c>
       <c r="BP109" s="62">
-        <v>0.85399999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="BQ109" s="43">
-        <v>0.65300000000000002</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="BR109" s="54">
-        <v>0.39500000000000002</v>
+        <v>0.66200000000000003</v>
       </c>
       <c r="BS109" s="62">
-        <v>0.82399999999999995</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="BT109" s="43">
-        <v>0.57499999999999996</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="BU109" s="54">
-        <v>0.33700000000000002</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="BV109" s="62">
-        <v>0.68200000000000005</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="BW109" s="43">
-        <v>0.50900000000000001</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="BX109" s="54">
-        <v>0.34300000000000003</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="BY109" s="45"/>
       <c r="BZ109" s="45"/>
@@ -8431,31 +8419,31 @@
         <v>20</v>
       </c>
       <c r="CE109" s="62">
-        <v>0.505</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="CF109" s="43">
+        <v>0.433</v>
+      </c>
+      <c r="CG109" s="54">
         <v>0.29099999999999998</v>
       </c>
-      <c r="CG109" s="54">
-        <v>0.22700000000000001</v>
-      </c>
       <c r="CH109" s="62">
-        <v>0.38600000000000001</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="CI109" s="43">
-        <v>0.26300000000000001</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="CJ109" s="54">
-        <v>0.191</v>
+        <v>0.252</v>
       </c>
       <c r="CK109" s="59">
-        <v>0.39500000000000002</v>
+        <v>0.45</v>
       </c>
       <c r="CL109" s="43">
-        <v>0.26500000000000001</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="CM109" s="54">
-        <v>0.17100000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="CN109" s="42"/>
       <c r="CO109" s="42"/>
@@ -8465,31 +8453,31 @@
         <v>20</v>
       </c>
       <c r="CS109" s="62">
-        <v>0.34200000000000003</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="CT109" s="43">
-        <v>0.21099999999999999</v>
+        <v>0.251</v>
       </c>
       <c r="CU109" s="54">
+        <v>0.186</v>
+      </c>
+      <c r="CV109" s="62">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="CW109" s="43">
         <v>0.192</v>
       </c>
-      <c r="CV109" s="62">
-        <v>0.26200000000000001</v>
-      </c>
-      <c r="CW109" s="43">
-        <v>0.186</v>
-      </c>
       <c r="CX109" s="54">
-        <v>0.11600000000000001</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="CY109" s="59">
-        <v>0.25800000000000001</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="CZ109" s="43">
-        <v>0.16200000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="DA109" s="54">
-        <v>0.10100000000000001</v>
+        <v>0.113</v>
       </c>
       <c r="DB109" s="42"/>
       <c r="DC109" s="42"/>
@@ -8503,31 +8491,31 @@
         <v>20</v>
       </c>
       <c r="DK109" s="62">
-        <v>0.80900000000000005</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="DL109" s="43">
-        <v>0.66700000000000004</v>
+        <v>0.77</v>
       </c>
       <c r="DM109" s="54">
-        <v>0.42399999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="DN109" s="62">
-        <v>0.81200000000000006</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="DO109" s="43">
-        <v>0.58899999999999997</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="DP109" s="54">
-        <v>0.372</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="DQ109" s="59">
-        <v>0.79200000000000004</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="DR109" s="43">
-        <v>0.58799999999999997</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="DS109" s="54">
-        <v>0.41599999999999998</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="DT109" s="42"/>
       <c r="DU109" s="42"/>
@@ -8537,31 +8525,31 @@
         <v>20</v>
       </c>
       <c r="DY109" s="62">
-        <v>0.53800000000000003</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="DZ109" s="43">
-        <v>0.31</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="EA109" s="54">
-        <v>0.23</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="EB109" s="62">
-        <v>0.50600000000000001</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="EC109" s="43">
-        <v>0.32400000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="ED109" s="54">
-        <v>0.247</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="EE109" s="59">
-        <v>0.54300000000000004</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="EF109" s="43">
-        <v>0.35699999999999998</v>
+        <v>0.37</v>
       </c>
       <c r="EG109" s="54">
-        <v>0.24399999999999999</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="EH109" s="42"/>
       <c r="EI109" s="42"/>
@@ -8570,37 +8558,37 @@
         <v>20</v>
       </c>
       <c r="EL109" s="62">
-        <v>0.38200000000000001</v>
+        <v>0.437</v>
       </c>
       <c r="EM109" s="43">
-        <v>0.22600000000000001</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="EN109" s="54">
-        <v>0.20200000000000001</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="EO109" s="62">
-        <v>0.33700000000000002</v>
+        <v>0.35799999999999998</v>
       </c>
       <c r="EP109" s="43">
-        <v>0.23200000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="EQ109" s="54">
-        <v>0.152</v>
+        <v>0.161</v>
       </c>
       <c r="ER109" s="59">
-        <v>0.35599999999999998</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="ES109" s="43">
-        <v>0.24299999999999999</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="ET109" s="54">
-        <v>0.16900000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="EU109" s="42"/>
       <c r="EV109" s="42"/>
       <c r="EW109" s="42"/>
     </row>
-    <row r="110" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="110" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M110" s="4" t="s">
         <v>21</v>
       </c>
@@ -8634,98 +8622,98 @@
       <c r="Z110" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA110" s="79">
+      <c r="AA110" s="75">
         <v>0.83399999999999996</v>
       </c>
-      <c r="AB110" s="80">
+      <c r="AB110" s="76">
         <v>0.83</v>
       </c>
-      <c r="AC110" s="72">
+      <c r="AC110" s="68">
         <v>0.84899999999999998</v>
       </c>
-      <c r="AD110" s="79">
+      <c r="AD110" s="75">
         <v>0.75600000000000001</v>
       </c>
-      <c r="AE110" s="80">
+      <c r="AE110" s="76">
         <v>0.66100000000000003</v>
       </c>
-      <c r="AF110" s="72">
+      <c r="AF110" s="68">
         <v>0.77200000000000002</v>
       </c>
-      <c r="AG110" s="79">
+      <c r="AG110" s="75">
         <v>0.68899999999999995</v>
       </c>
-      <c r="AH110" s="80">
+      <c r="AH110" s="76">
         <v>0.68600000000000005</v>
       </c>
-      <c r="AI110" s="72">
+      <c r="AI110" s="68">
         <v>0.69399999999999995</v>
       </c>
-      <c r="AJ110" s="82"/>
-      <c r="AK110" s="82"/>
-      <c r="AL110" s="82"/>
+      <c r="AJ110" s="78"/>
+      <c r="AK110" s="78"/>
+      <c r="AL110" s="78"/>
       <c r="AM110" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AN110" s="79">
+      <c r="AN110" s="75">
         <v>0.48799999999999999</v>
       </c>
-      <c r="AO110" s="80">
+      <c r="AO110" s="76">
         <v>0.48299999999999998</v>
       </c>
-      <c r="AP110" s="72">
+      <c r="AP110" s="68">
         <v>0.45600000000000002</v>
       </c>
-      <c r="AQ110" s="79">
+      <c r="AQ110" s="75">
         <v>0.47899999999999998</v>
       </c>
-      <c r="AR110" s="80">
+      <c r="AR110" s="76">
         <v>0.497</v>
       </c>
-      <c r="AS110" s="72">
+      <c r="AS110" s="68">
         <v>0.48199999999999998</v>
       </c>
-      <c r="AT110" s="79">
+      <c r="AT110" s="75">
         <v>0.46500000000000002</v>
       </c>
-      <c r="AU110" s="80">
+      <c r="AU110" s="76">
         <v>0.42899999999999999</v>
       </c>
-      <c r="AV110" s="72">
+      <c r="AV110" s="68">
         <v>0.42199999999999999</v>
       </c>
-      <c r="AW110" s="71"/>
-      <c r="AX110" s="71"/>
-      <c r="AY110" s="71"/>
-      <c r="AZ110" s="71"/>
+      <c r="AW110" s="67"/>
+      <c r="AX110" s="67"/>
+      <c r="AY110" s="67"/>
+      <c r="AZ110" s="67"/>
       <c r="BA110" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="BB110" s="79">
+      <c r="BB110" s="75">
         <v>0.32300000000000001</v>
       </c>
-      <c r="BC110" s="80">
+      <c r="BC110" s="76">
         <v>0.32200000000000001</v>
       </c>
-      <c r="BD110" s="72">
+      <c r="BD110" s="68">
         <v>0.29599999999999999</v>
       </c>
-      <c r="BE110" s="79">
+      <c r="BE110" s="75">
         <v>0.27600000000000002</v>
       </c>
-      <c r="BF110" s="80">
+      <c r="BF110" s="76">
         <v>0.27</v>
       </c>
-      <c r="BG110" s="72">
+      <c r="BG110" s="68">
         <v>0.25700000000000001</v>
       </c>
-      <c r="BH110" s="79">
+      <c r="BH110" s="75">
         <v>0.27600000000000002</v>
       </c>
-      <c r="BI110" s="80">
+      <c r="BI110" s="76">
         <v>0.28100000000000003</v>
       </c>
-      <c r="BJ110" s="72">
+      <c r="BJ110" s="68">
         <v>0.25900000000000001</v>
       </c>
       <c r="BO110" s="49" t="s">
@@ -8936,7 +8924,7 @@
       <c r="EV110" s="42"/>
       <c r="EW110" s="42"/>
     </row>
-    <row r="111" spans="13:153" ht="24.9" customHeight="1">
+    <row r="111" spans="13:153" ht="24.95" customHeight="1">
       <c r="M111" s="2" t="s">
         <v>12</v>
       </c>
@@ -8970,98 +8958,98 @@
       <c r="Z111" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA111" s="83">
+      <c r="AA111" s="79">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AB111" s="84">
+      <c r="AB111" s="80">
         <v>0.85399999999999998</v>
       </c>
-      <c r="AC111" s="85">
+      <c r="AC111" s="81">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AD111" s="83">
+      <c r="AD111" s="79">
         <v>0.77100000000000002</v>
       </c>
-      <c r="AE111" s="84">
+      <c r="AE111" s="80">
         <v>0.77900000000000003</v>
       </c>
-      <c r="AF111" s="85">
+      <c r="AF111" s="81">
         <v>0.80300000000000005</v>
       </c>
-      <c r="AG111" s="83">
+      <c r="AG111" s="79">
         <v>0.76500000000000001</v>
       </c>
-      <c r="AH111" s="84">
+      <c r="AH111" s="80">
         <v>0.746</v>
       </c>
-      <c r="AI111" s="85">
+      <c r="AI111" s="81">
         <v>0.69499999999999995</v>
       </c>
-      <c r="AJ111" s="82"/>
-      <c r="AK111" s="82"/>
-      <c r="AL111" s="82"/>
+      <c r="AJ111" s="78"/>
+      <c r="AK111" s="78"/>
+      <c r="AL111" s="78"/>
       <c r="AM111" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="AN111" s="83">
+      <c r="AN111" s="79">
         <v>0.52400000000000002</v>
       </c>
-      <c r="AO111" s="84">
+      <c r="AO111" s="80">
         <v>0.49199999999999999</v>
       </c>
-      <c r="AP111" s="85">
+      <c r="AP111" s="81">
         <v>0.47</v>
       </c>
-      <c r="AQ111" s="83">
+      <c r="AQ111" s="79">
         <v>0.496</v>
       </c>
-      <c r="AR111" s="84">
+      <c r="AR111" s="80">
         <v>0.49099999999999999</v>
       </c>
-      <c r="AS111" s="85">
+      <c r="AS111" s="81">
         <v>0.47899999999999998</v>
       </c>
-      <c r="AT111" s="83">
+      <c r="AT111" s="79">
         <v>0.496</v>
       </c>
-      <c r="AU111" s="84">
+      <c r="AU111" s="80">
         <v>0.49299999999999999</v>
       </c>
-      <c r="AV111" s="85">
+      <c r="AV111" s="81">
         <v>0.48599999999999999</v>
       </c>
-      <c r="AW111" s="71"/>
-      <c r="AX111" s="71"/>
-      <c r="AY111" s="71"/>
-      <c r="AZ111" s="71"/>
+      <c r="AW111" s="67"/>
+      <c r="AX111" s="67"/>
+      <c r="AY111" s="67"/>
+      <c r="AZ111" s="67"/>
       <c r="BA111" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="BB111" s="73">
+      <c r="BB111" s="69">
         <v>0.34300000000000003</v>
       </c>
-      <c r="BC111" s="74">
+      <c r="BC111" s="70">
         <v>0.33300000000000002</v>
       </c>
-      <c r="BD111" s="75">
+      <c r="BD111" s="71">
         <v>0.29099999999999998</v>
       </c>
-      <c r="BE111" s="73">
+      <c r="BE111" s="69">
         <v>0.249</v>
       </c>
-      <c r="BF111" s="74">
+      <c r="BF111" s="70">
         <v>0.246</v>
       </c>
-      <c r="BG111" s="75">
+      <c r="BG111" s="71">
         <v>0.253</v>
       </c>
-      <c r="BH111" s="73">
+      <c r="BH111" s="69">
         <v>0.26300000000000001</v>
       </c>
-      <c r="BI111" s="74">
+      <c r="BI111" s="70">
         <v>0.26900000000000002</v>
       </c>
-      <c r="BJ111" s="75">
+      <c r="BJ111" s="71">
         <v>0.26900000000000002</v>
       </c>
       <c r="BO111" s="50" t="s">
@@ -9272,7 +9260,7 @@
       <c r="EV111" s="42"/>
       <c r="EW111" s="42"/>
     </row>
-    <row r="112" spans="13:153" ht="24.9" customHeight="1">
+    <row r="112" spans="13:153" ht="24.95" customHeight="1">
       <c r="M112" s="3" t="s">
         <v>19</v>
       </c>
@@ -9306,98 +9294,98 @@
       <c r="Z112" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AA112" s="76">
+      <c r="AA112" s="72">
         <v>0.83199999999999996</v>
       </c>
-      <c r="AB112" s="77">
+      <c r="AB112" s="73">
         <v>0.84199999999999997</v>
       </c>
-      <c r="AC112" s="78">
+      <c r="AC112" s="74">
         <v>0.83599999999999997</v>
       </c>
-      <c r="AD112" s="76">
+      <c r="AD112" s="72">
         <v>0.76500000000000001</v>
       </c>
-      <c r="AE112" s="77">
+      <c r="AE112" s="73">
         <v>0.72799999999999998</v>
       </c>
-      <c r="AF112" s="78">
+      <c r="AF112" s="74">
         <v>0.66300000000000003</v>
       </c>
-      <c r="AG112" s="76">
+      <c r="AG112" s="72">
         <v>0.69499999999999995</v>
       </c>
-      <c r="AH112" s="77">
+      <c r="AH112" s="73">
         <v>0.66400000000000003</v>
       </c>
-      <c r="AI112" s="78">
+      <c r="AI112" s="74">
         <v>0.63800000000000001</v>
       </c>
-      <c r="AJ112" s="82"/>
-      <c r="AK112" s="82"/>
-      <c r="AL112" s="82"/>
+      <c r="AJ112" s="78"/>
+      <c r="AK112" s="78"/>
+      <c r="AL112" s="78"/>
       <c r="AM112" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="AN112" s="76">
+      <c r="AN112" s="72">
         <v>0.50700000000000001</v>
       </c>
-      <c r="AO112" s="77">
+      <c r="AO112" s="73">
         <v>0.49199999999999999</v>
       </c>
-      <c r="AP112" s="78">
+      <c r="AP112" s="74">
         <v>0.45500000000000002</v>
       </c>
-      <c r="AQ112" s="76">
+      <c r="AQ112" s="72">
         <v>0.39800000000000002</v>
       </c>
-      <c r="AR112" s="77">
+      <c r="AR112" s="73">
         <v>0.35799999999999998</v>
       </c>
-      <c r="AS112" s="78">
+      <c r="AS112" s="74">
         <v>0.33700000000000002</v>
       </c>
-      <c r="AT112" s="76">
+      <c r="AT112" s="72">
         <v>0.372</v>
       </c>
-      <c r="AU112" s="77">
+      <c r="AU112" s="73">
         <v>0.34399999999999997</v>
       </c>
-      <c r="AV112" s="78">
+      <c r="AV112" s="74">
         <v>0.33500000000000002</v>
       </c>
-      <c r="AW112" s="71"/>
-      <c r="AX112" s="71"/>
-      <c r="AY112" s="71"/>
-      <c r="AZ112" s="71"/>
+      <c r="AW112" s="67"/>
+      <c r="AX112" s="67"/>
+      <c r="AY112" s="67"/>
+      <c r="AZ112" s="67"/>
       <c r="BA112" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="BB112" s="76">
+      <c r="BB112" s="72">
         <v>0.32</v>
       </c>
-      <c r="BC112" s="77">
+      <c r="BC112" s="73">
         <v>0.313</v>
       </c>
-      <c r="BD112" s="78">
+      <c r="BD112" s="74">
         <v>0.28799999999999998</v>
       </c>
-      <c r="BE112" s="76">
+      <c r="BE112" s="72">
         <v>0.249</v>
       </c>
-      <c r="BF112" s="77">
+      <c r="BF112" s="73">
         <v>0.24099999999999999</v>
       </c>
-      <c r="BG112" s="78">
+      <c r="BG112" s="74">
         <v>0.22</v>
       </c>
-      <c r="BH112" s="76">
+      <c r="BH112" s="72">
         <v>0.25</v>
       </c>
-      <c r="BI112" s="77">
+      <c r="BI112" s="73">
         <v>0.24399999999999999</v>
       </c>
-      <c r="BJ112" s="78">
+      <c r="BJ112" s="74">
         <v>0.24099999999999999</v>
       </c>
       <c r="BO112" s="48" t="s">
@@ -9608,163 +9596,163 @@
       <c r="EV112" s="42"/>
       <c r="EW112" s="42"/>
     </row>
-    <row r="113" spans="13:153" ht="24.9" customHeight="1">
+    <row r="113" spans="13:153" ht="24.95" customHeight="1">
       <c r="M113" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N113" s="32">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="O113" s="33">
+        <v>0</v>
+      </c>
+      <c r="P113" s="34">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="Q113" s="32">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="R113" s="33">
         <v>0.16700000000000001</v>
       </c>
-      <c r="O113" s="33">
-        <v>0.104</v>
-      </c>
-      <c r="P113" s="34">
-        <v>0.23100000000000001</v>
-      </c>
-      <c r="Q113" s="32">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="R113" s="33">
-        <v>0.13700000000000001</v>
-      </c>
       <c r="S113" s="34">
-        <v>0.14299999999999999</v>
+        <v>0.184</v>
       </c>
       <c r="T113" s="32">
-        <v>0.13900000000000001</v>
+        <v>0.152</v>
       </c>
       <c r="U113" s="33">
-        <v>0.14899999999999999</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="V113" s="34">
-        <v>0.13400000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="Z113" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AA113" s="76">
-        <v>0.42199999999999999</v>
-      </c>
-      <c r="AB113" s="77">
-        <v>0.67600000000000005</v>
-      </c>
-      <c r="AC113" s="78">
-        <v>0.70699999999999996</v>
-      </c>
-      <c r="AD113" s="76">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="AE113" s="77">
-        <v>0.68400000000000005</v>
-      </c>
-      <c r="AF113" s="78">
-        <v>0.70499999999999996</v>
-      </c>
-      <c r="AG113" s="76">
-        <v>0.57699999999999996</v>
-      </c>
-      <c r="AH113" s="77">
-        <v>0.629</v>
-      </c>
-      <c r="AI113" s="78">
-        <v>0.69099999999999995</v>
-      </c>
-      <c r="AJ113" s="82"/>
-      <c r="AK113" s="82"/>
-      <c r="AL113" s="82"/>
+      <c r="AA113" s="72">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="AB113" s="73">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="AC113" s="74">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="AD113" s="72">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="AE113" s="73">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="AF113" s="74">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="AG113" s="72">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="AH113" s="73">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="AI113" s="74">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="AJ113" s="78"/>
+      <c r="AK113" s="78"/>
+      <c r="AL113" s="78"/>
       <c r="AM113" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="AN113" s="76">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="AO113" s="77">
-        <v>0.31</v>
-      </c>
-      <c r="AP113" s="78">
-        <v>0.34300000000000003</v>
-      </c>
-      <c r="AQ113" s="76">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="AR113" s="77">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="AS113" s="78">
-        <v>0.30299999999999999</v>
-      </c>
-      <c r="AT113" s="76">
-        <v>0.373</v>
-      </c>
-      <c r="AU113" s="77">
-        <v>0.371</v>
-      </c>
-      <c r="AV113" s="78">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="AW113" s="71"/>
-      <c r="AX113" s="71"/>
-      <c r="AY113" s="71"/>
-      <c r="AZ113" s="71"/>
+      <c r="AN113" s="72">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="AO113" s="73">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="AP113" s="74">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="AQ113" s="72">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="AR113" s="73">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="AS113" s="74">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="AT113" s="72">
+        <v>0.377</v>
+      </c>
+      <c r="AU113" s="73">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="AV113" s="74">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="AW113" s="67"/>
+      <c r="AX113" s="67"/>
+      <c r="AY113" s="67"/>
+      <c r="AZ113" s="67"/>
       <c r="BA113" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="BB113" s="76">
-        <v>0.126</v>
-      </c>
-      <c r="BC113" s="77">
-        <v>0.114</v>
-      </c>
-      <c r="BD113" s="78">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="BE113" s="76">
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="BF113" s="77">
-        <v>0.192</v>
-      </c>
-      <c r="BG113" s="78">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="BH113" s="76">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="BI113" s="77">
-        <v>0.23</v>
-      </c>
-      <c r="BJ113" s="78">
-        <v>0.20599999999999999</v>
+      <c r="BB113" s="72">
+        <v>0.159</v>
+      </c>
+      <c r="BC113" s="73">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="BD113" s="74">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="BE113" s="72">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="BF113" s="73">
+        <v>0.2</v>
+      </c>
+      <c r="BG113" s="74">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="BH113" s="72">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="BI113" s="73">
+        <v>0.251</v>
+      </c>
+      <c r="BJ113" s="74">
+        <v>0.24199999999999999</v>
       </c>
       <c r="BO113" s="48" t="s">
         <v>13</v>
       </c>
       <c r="BP113" s="62">
-        <v>0.95</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="BQ113" s="43">
-        <v>0.755</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="BR113" s="54">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="BS113" s="62">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="BT113" s="43">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="BU113" s="54">
         <v>0.33</v>
       </c>
-      <c r="BS113" s="62">
-        <v>0.94</v>
-      </c>
-      <c r="BT113" s="43">
-        <v>0.749</v>
-      </c>
-      <c r="BU113" s="54">
-        <v>0.30199999999999999</v>
-      </c>
       <c r="BV113" s="62">
-        <v>0.94699999999999995</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="BW113" s="43">
-        <v>0.56999999999999995</v>
+        <v>0.443</v>
       </c>
       <c r="BX113" s="54">
-        <v>0.33700000000000002</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="BY113" s="45"/>
       <c r="BZ113" s="45"/>
@@ -9775,31 +9763,31 @@
         <v>13</v>
       </c>
       <c r="CE113" s="62">
-        <v>0.56699999999999995</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="CF113" s="43">
-        <v>0.28399999999999997</v>
+        <v>0.371</v>
       </c>
       <c r="CG113" s="54">
-        <v>0.23200000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="CH113" s="62">
-        <v>0.45100000000000001</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="CI113" s="43">
-        <v>0.17100000000000001</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="CJ113" s="54">
-        <v>0.15</v>
+        <v>0.217</v>
       </c>
       <c r="CK113" s="59">
-        <v>0.58099999999999996</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="CL113" s="43">
-        <v>0.27200000000000002</v>
+        <v>0.221</v>
       </c>
       <c r="CM113" s="54">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="CN113" s="42"/>
       <c r="CO113" s="42"/>
@@ -9809,31 +9797,31 @@
         <v>13</v>
       </c>
       <c r="CS113" s="62">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="CT113" s="43">
         <v>0</v>
       </c>
-      <c r="CT113" s="43">
-        <v>0.104</v>
-      </c>
       <c r="CU113" s="54">
-        <v>0.192</v>
+        <v>0</v>
       </c>
       <c r="CV113" s="62">
-        <v>0.26</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="CW113" s="43">
-        <v>0.13700000000000001</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="CX113" s="54">
-        <v>0.156</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="CY113" s="59">
-        <v>0.17799999999999999</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="CZ113" s="43">
-        <v>0.14899999999999999</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="DA113" s="54">
-        <v>6.8000000000000005E-2</v>
+        <v>0.129</v>
       </c>
       <c r="DB113" s="42"/>
       <c r="DC113" s="42"/>
@@ -9847,31 +9835,31 @@
         <v>13</v>
       </c>
       <c r="DK113" s="62">
-        <v>0.91100000000000003</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="DL113" s="43">
-        <v>0.67600000000000005</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="DM113" s="54">
-        <v>0.377</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="DN113" s="62">
-        <v>0.89900000000000002</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="DO113" s="43">
-        <v>0.68400000000000005</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="DP113" s="54">
-        <v>0.36499999999999999</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="DQ113" s="59">
-        <v>0.91900000000000004</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="DR113" s="43">
-        <v>0.629</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="DS113" s="54">
-        <v>0.41799999999999998</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="DT113" s="42"/>
       <c r="DU113" s="42"/>
@@ -9881,31 +9869,31 @@
         <v>13</v>
       </c>
       <c r="DY113" s="62">
-        <v>0.59699999999999998</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="DZ113" s="43">
-        <v>0.31</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="EA113" s="54">
-        <v>0.24299999999999999</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="EB113" s="62">
-        <v>0.53500000000000003</v>
+        <v>0.499</v>
       </c>
       <c r="EC113" s="43">
-        <v>0.26500000000000001</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="ED113" s="54">
-        <v>0.20499999999999999</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="EE113" s="59">
-        <v>0.64600000000000002</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="EF113" s="43">
-        <v>0.371</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="EG113" s="54">
-        <v>0.248</v>
+        <v>0.251</v>
       </c>
       <c r="EH113" s="42"/>
       <c r="EI113" s="42"/>
@@ -9914,37 +9902,37 @@
         <v>13</v>
       </c>
       <c r="EL113" s="62">
-        <v>1E-3</v>
+        <v>0.309</v>
       </c>
       <c r="EM113" s="43">
-        <v>0.114</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="EN113" s="54">
-        <v>0.16400000000000001</v>
+        <v>2E-3</v>
       </c>
       <c r="EO113" s="62">
-        <v>0.33400000000000002</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="EP113" s="43">
-        <v>0.192</v>
+        <v>0.2</v>
       </c>
       <c r="EQ113" s="54">
-        <v>0.159</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="ER113" s="59">
-        <v>0.29499999999999998</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="ES113" s="43">
-        <v>0.23</v>
+        <v>0.251</v>
       </c>
       <c r="ET113" s="54">
-        <v>0.14899999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="EU113" s="42"/>
       <c r="EV113" s="42"/>
       <c r="EW113" s="42"/>
     </row>
-    <row r="114" spans="13:153" ht="24.9" customHeight="1" thickBot="1">
+    <row r="114" spans="13:153" ht="24.95" customHeight="1" thickBot="1">
       <c r="M114" s="4" t="s">
         <v>14</v>
       </c>
@@ -9978,98 +9966,98 @@
       <c r="Z114" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AA114" s="79">
+      <c r="AA114" s="75">
         <v>0.82099999999999995</v>
       </c>
-      <c r="AB114" s="80">
+      <c r="AB114" s="76">
         <v>0.83299999999999996</v>
       </c>
-      <c r="AC114" s="72">
+      <c r="AC114" s="68">
         <v>0.85199999999999998</v>
       </c>
-      <c r="AD114" s="79">
+      <c r="AD114" s="75">
         <v>0.75900000000000001</v>
       </c>
-      <c r="AE114" s="80">
+      <c r="AE114" s="76">
         <v>0.76200000000000001</v>
       </c>
-      <c r="AF114" s="72">
+      <c r="AF114" s="68">
         <v>0.78600000000000003</v>
       </c>
-      <c r="AG114" s="79">
+      <c r="AG114" s="75">
         <v>0.74299999999999999</v>
       </c>
-      <c r="AH114" s="80">
+      <c r="AH114" s="76">
         <v>0.69699999999999995</v>
       </c>
-      <c r="AI114" s="72">
+      <c r="AI114" s="68">
         <v>0.68300000000000005</v>
       </c>
-      <c r="AJ114" s="82"/>
-      <c r="AK114" s="82"/>
-      <c r="AL114" s="82"/>
+      <c r="AJ114" s="78"/>
+      <c r="AK114" s="78"/>
+      <c r="AL114" s="78"/>
       <c r="AM114" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="AN114" s="79">
+      <c r="AN114" s="75">
         <v>0.49</v>
       </c>
-      <c r="AO114" s="80">
+      <c r="AO114" s="76">
         <v>0.46899999999999997</v>
       </c>
-      <c r="AP114" s="72">
+      <c r="AP114" s="68">
         <v>0.45</v>
       </c>
-      <c r="AQ114" s="79">
+      <c r="AQ114" s="75">
         <v>0.46700000000000003</v>
       </c>
-      <c r="AR114" s="80">
+      <c r="AR114" s="76">
         <v>0.48599999999999999</v>
       </c>
-      <c r="AS114" s="72">
+      <c r="AS114" s="68">
         <v>0.47799999999999998</v>
       </c>
-      <c r="AT114" s="79">
+      <c r="AT114" s="75">
         <v>0.48299999999999998</v>
       </c>
-      <c r="AU114" s="80">
+      <c r="AU114" s="76">
         <v>0.48399999999999999</v>
       </c>
-      <c r="AV114" s="72">
+      <c r="AV114" s="68">
         <v>0.47</v>
       </c>
-      <c r="AW114" s="71"/>
-      <c r="AX114" s="71"/>
-      <c r="AY114" s="71"/>
-      <c r="AZ114" s="71"/>
+      <c r="AW114" s="67"/>
+      <c r="AX114" s="67"/>
+      <c r="AY114" s="67"/>
+      <c r="AZ114" s="67"/>
       <c r="BA114" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="BB114" s="79">
+      <c r="BB114" s="75">
         <v>0.33500000000000002</v>
       </c>
-      <c r="BC114" s="80">
+      <c r="BC114" s="76">
         <v>0.32900000000000001</v>
       </c>
-      <c r="BD114" s="72">
+      <c r="BD114" s="68">
         <v>0.30199999999999999</v>
       </c>
-      <c r="BE114" s="79">
+      <c r="BE114" s="75">
         <v>0.27</v>
       </c>
-      <c r="BF114" s="80">
+      <c r="BF114" s="76">
         <v>0.253</v>
       </c>
-      <c r="BG114" s="72">
+      <c r="BG114" s="68">
         <v>0.255</v>
       </c>
-      <c r="BH114" s="79">
+      <c r="BH114" s="75">
         <v>0.26500000000000001</v>
       </c>
-      <c r="BI114" s="80">
+      <c r="BI114" s="76">
         <v>0.26900000000000002</v>
       </c>
-      <c r="BJ114" s="72">
+      <c r="BJ114" s="68">
         <v>0.26200000000000001</v>
       </c>
       <c r="BO114" s="49" t="s">
@@ -10110,31 +10098,31 @@
       <c r="CD114" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="CE114" s="69">
+      <c r="CE114" s="63">
         <v>0.55800000000000005</v>
       </c>
-      <c r="CF114" s="66">
+      <c r="CF114" s="55">
         <v>0.39700000000000002</v>
       </c>
-      <c r="CG114" s="67">
+      <c r="CG114" s="56">
         <v>0.32300000000000001</v>
       </c>
-      <c r="CH114" s="69">
+      <c r="CH114" s="63">
         <v>0.63200000000000001</v>
       </c>
-      <c r="CI114" s="66">
+      <c r="CI114" s="55">
         <v>0.438</v>
       </c>
-      <c r="CJ114" s="67">
+      <c r="CJ114" s="56">
         <v>0.27800000000000002</v>
       </c>
-      <c r="CK114" s="68">
+      <c r="CK114" s="60">
         <v>0.47299999999999998</v>
       </c>
-      <c r="CL114" s="66">
+      <c r="CL114" s="55">
         <v>0.442</v>
       </c>
-      <c r="CM114" s="67">
+      <c r="CM114" s="56">
         <v>0.23300000000000001</v>
       </c>
       <c r="CN114" s="42"/>
@@ -10622,18 +10610,18 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="N40:V40"/>
+    <mergeCell ref="N92:V92"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="Q93:S93"/>
+    <mergeCell ref="T93:V93"/>
     <mergeCell ref="T41:V41"/>
     <mergeCell ref="N67:P67"/>
     <mergeCell ref="Q67:S67"/>
     <mergeCell ref="T67:V67"/>
     <mergeCell ref="N93:P93"/>
     <mergeCell ref="N66:V66"/>
-    <mergeCell ref="N40:V40"/>
-    <mergeCell ref="N92:V92"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="Q93:S93"/>
-    <mergeCell ref="T93:V93"/>
     <mergeCell ref="AA92:AI92"/>
     <mergeCell ref="AA93:AC93"/>
     <mergeCell ref="AD93:AF93"/>
@@ -10671,6 +10659,18 @@
     <mergeCell ref="EB93:ED93"/>
     <mergeCell ref="EE93:EG93"/>
   </mergeCells>
+  <conditionalFormatting sqref="K13:L24 W13:X24 M95:V114 M69:V88 N43:V62">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M43:M62">
     <cfRule type="colorScale" priority="27">
       <colorScale>
@@ -10851,19 +10851,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:L24 W13:X24 M95:V114 M69:V88 N43:V62">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="85" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>